--- a/AAII_Financials/Quarterly/PRDO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRDO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
   <si>
     <t>PRDO</t>
   </si>
@@ -656,353 +656,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>147900</v>
+      </c>
+      <c r="E8" s="3">
         <v>179900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>186600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>195600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>176100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>168400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>167700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>183000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>159900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>174000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>175500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>183600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>171200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>169100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>176000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>171000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>158500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>155000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>156400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>157900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>145500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>145700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>142000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>148100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>143100</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E9" s="3">
         <v>33500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>32700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>33900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>31200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>30100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>27300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>28100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>25300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>26000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>28500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>29000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>28600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>27600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>28700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>26900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>24900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>25300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>25400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>26300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>25500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>27200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>30300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>26900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>117700</v>
+      </c>
+      <c r="E10" s="3">
         <v>146400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>153900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>161700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>144900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>138300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>140400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>154900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>134600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>148000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>147000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>154600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>142600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>141500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>147300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>144100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>133600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>129700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>131100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>131600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>120000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>118500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>111700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>121200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>114100</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1030,8 +1042,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1107,8 +1120,11 @@
       <c r="AA12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,35 +1200,38 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E14" s="3">
         <v>7400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2800</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1225,17 +1244,17 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>600</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1246,11 +1265,11 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
@@ -1258,46 +1277,49 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E15" s="3">
         <v>3900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5100</v>
-      </c>
-      <c r="I15" s="3">
-        <v>4900</v>
       </c>
       <c r="J15" s="3">
         <v>4900</v>
       </c>
       <c r="K15" s="3">
+        <v>4900</v>
+      </c>
+      <c r="L15" s="3">
         <v>5000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>3900</v>
       </c>
       <c r="M15" s="3">
         <v>3900</v>
       </c>
       <c r="N15" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="O15" s="3">
         <v>4000</v>
@@ -1306,40 +1328,43 @@
         <v>4000</v>
       </c>
       <c r="Q15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="R15" s="3">
         <v>4200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2300</v>
-      </c>
-      <c r="U15" s="3">
-        <v>2200</v>
       </c>
       <c r="V15" s="3">
         <v>2200</v>
       </c>
       <c r="W15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="X15" s="3">
         <v>2300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2100</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>2600</v>
       </c>
       <c r="AA15" s="3">
         <v>2600</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>132000</v>
+      </c>
+      <c r="E17" s="3">
         <v>136900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>138500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>152300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>153500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>139100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>133700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>139300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>125300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>136100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>139600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>143000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>135000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>137100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>138700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>133700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>126400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>130700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>156300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>127900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>125300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>126400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>130700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>127500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>132400</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E18" s="3">
         <v>43100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>48100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>43300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>22600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>29300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>34000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>43700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>34600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>37900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>35900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>40600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>36200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>32000</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>37300</v>
       </c>
       <c r="R18" s="3">
         <v>37300</v>
       </c>
       <c r="S18" s="3">
+        <v>37300</v>
+      </c>
+      <c r="T18" s="3">
         <v>32100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>24300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>30000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>20200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>19300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>11300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>20600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,162 +1579,169 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E20" s="3">
         <v>5100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>26600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>900</v>
-      </c>
-      <c r="J20" s="3">
-        <v>200</v>
       </c>
       <c r="K20" s="3">
         <v>200</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>500</v>
-      </c>
-      <c r="O20" s="3">
-        <v>700</v>
       </c>
       <c r="P20" s="3">
         <v>700</v>
       </c>
       <c r="Q20" s="3">
+        <v>700</v>
+      </c>
+      <c r="R20" s="3">
         <v>1200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E21" s="3">
         <v>52100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>79100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>52300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>29400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>36500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>39700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>48800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>39700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>41800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>40200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>45100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>40900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>36800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>42700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>41400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>36000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>28400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>33900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>23700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>22600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>14000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>24100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>14100</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1727,21 +1766,21 @@
       <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="K22" s="3">
+        <v>100</v>
+      </c>
+      <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
@@ -1764,10 +1803,10 @@
         <v>0</v>
       </c>
       <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
         <v>400</v>
-      </c>
-      <c r="X22" s="3">
-        <v>100</v>
       </c>
       <c r="Y22" s="3">
         <v>100</v>
@@ -1778,162 +1817,171 @@
       <c r="AA22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E23" s="3">
         <v>48100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>74600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>47100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>24400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>31300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>34700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>43800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>34800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>37300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>36000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>41000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>36900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>32800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>38500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>38700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>33600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>26000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>31600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>21000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>20200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>11800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>21400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E24" s="3">
         <v>6800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>19900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>12600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>9200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>11800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>10300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>10200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>10300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>9600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>6100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E26" s="3">
         <v>41300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>54700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>34500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>16000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>22100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>25800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>32100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>24500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>27800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>26700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>30800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>27100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>40000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>28200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>29100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>27500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>18400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>25200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>14000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>15100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>8900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>17900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E27" s="3">
         <v>41300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>54700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>34500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>16000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>22100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>25800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>32100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>24500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>27800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>26700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>30800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>27100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>40000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>28200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>29100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>27500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>18400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>25200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>14000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>15100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>8900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>17900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2266,8 +2326,8 @@
       <c r="J29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -2294,31 +2354,34 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>-200</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>-400</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>100</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-200</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-100</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-400</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-52400</v>
       </c>
     </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,162 +2537,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-26600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-900</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-200</v>
       </c>
       <c r="K32" s="3">
         <v>-200</v>
       </c>
       <c r="L32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-500</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-700</v>
       </c>
       <c r="P32" s="3">
         <v>-700</v>
       </c>
       <c r="Q32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="R32" s="3">
         <v>-1200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E33" s="3">
         <v>41300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>54700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>34500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>16000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>22100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>25800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>32100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>24500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>27800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>26600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>30800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>27100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>39900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>28200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>29100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>27500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>18200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>24800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>14100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>14900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>8800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>17500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E35" s="3">
         <v>41300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>54700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>34500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>16000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>22100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>25800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>32100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>24500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>27800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>26600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>30800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>27100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>39900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>28200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>29100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>27500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>18200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>24800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>14100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>14900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>8800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>17500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,271 +3004,281 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E41" s="3">
         <v>165600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>140500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>411500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>109400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>147100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>148700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>190400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>320000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>266400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>87300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>86000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>105700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>58100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>91500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>37900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>108700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>47400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>51100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>38800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>32400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>32000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>33200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>24200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>485100</v>
+      </c>
+      <c r="E42" s="3">
         <v>429600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>428100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>99300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>399300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>375900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>366800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>307600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>174200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>209400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>389300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>361000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>300700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>305600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>250300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>243700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>185500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>234400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>228800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>200800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>196400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>156300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>151600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>158000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>156200</v>
       </c>
     </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E43" s="3">
         <v>53300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>49200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>49300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>46000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>45300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>40800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>42900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>44700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>44400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>54300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>44200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>47600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>40300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>37100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>34100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>56400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>31200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>30500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>32400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>31300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>36500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>26900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>25300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1200</v>
-      </c>
-      <c r="M44" s="3">
-        <v>600</v>
       </c>
       <c r="N44" s="3">
         <v>600</v>
@@ -3204,7 +3299,7 @@
         <v>600</v>
       </c>
       <c r="T44" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="U44" s="3">
         <v>700</v>
@@ -3213,193 +3308,202 @@
         <v>700</v>
       </c>
       <c r="W44" s="3">
+        <v>700</v>
+      </c>
+      <c r="X44" s="3">
         <v>800</v>
-      </c>
-      <c r="X44" s="3">
-        <v>900</v>
       </c>
       <c r="Y44" s="3">
         <v>900</v>
       </c>
       <c r="Z44" s="3">
+        <v>900</v>
+      </c>
+      <c r="AA44" s="3">
         <v>1000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E45" s="3">
         <v>18900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>22700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>21600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>18500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>14200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>15800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>17600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>12600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>14600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>16000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>39300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>9800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>9500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>14400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>18100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>16900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>15300</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>655000</v>
+      </c>
+      <c r="E46" s="3">
         <v>669600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>643400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>585400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>575100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>582300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>571800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>556200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>554500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>537100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>549100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>506100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>467100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>416900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>394100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>332300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>360400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>353000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>320900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>282200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>269400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>240100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>230700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>225400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>210700</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1200</v>
+        <v>3900</v>
       </c>
       <c r="E47" s="3">
         <v>1200</v>
       </c>
       <c r="F47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G47" s="3">
         <v>1500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1900</v>
-      </c>
-      <c r="H47" s="3">
-        <v>1300</v>
       </c>
       <c r="I47" s="3">
         <v>1300</v>
@@ -3408,185 +3512,191 @@
         <v>1300</v>
       </c>
       <c r="K47" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="L47" s="3">
         <v>1400</v>
       </c>
       <c r="M47" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N47" s="3">
         <v>1500</v>
-      </c>
-      <c r="N47" s="3">
-        <v>1300</v>
       </c>
       <c r="O47" s="3">
         <v>1300</v>
       </c>
       <c r="P47" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="Q47" s="3">
         <v>1200</v>
       </c>
       <c r="R47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="S47" s="3">
         <v>1100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E48" s="3">
         <v>45600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>47400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>50000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>52200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>56600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>59400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>62500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>65000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>64600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>65600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>68100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>72500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>75900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>77200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>79400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>76400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>78700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>67600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>71800</v>
-      </c>
-      <c r="W48" s="3">
-        <v>30000</v>
       </c>
       <c r="X48" s="3">
         <v>30000</v>
       </c>
       <c r="Y48" s="3">
+        <v>30000</v>
+      </c>
+      <c r="Z48" s="3">
         <v>30800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>32000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>33200</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>277400</v>
+      </c>
+      <c r="E49" s="3">
         <v>281100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>293200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>294900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>297100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>228400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>191500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>193100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>194800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>196800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>132200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>133000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>133800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>134700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>135500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>137100</v>
-      </c>
-      <c r="S49" s="3">
-        <v>95300</v>
       </c>
       <c r="T49" s="3">
         <v>95300</v>
@@ -3612,8 +3722,11 @@
       <c r="AA49" s="3">
         <v>95300</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>95300</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,85 +3882,91 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>28500</v>
+        <v>30600</v>
       </c>
       <c r="E52" s="3">
         <v>28500</v>
       </c>
       <c r="F52" s="3">
+        <v>28500</v>
+      </c>
+      <c r="G52" s="3">
         <v>31200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>31100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>30600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>32100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>30700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>31800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>36500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>38000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>41900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>46800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>55200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>47200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>56600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>65900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>70700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>77500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>80000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>86800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>93800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>99700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>101900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>105300</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,85 +4042,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1007300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1026000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1013700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>963000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>957400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>899200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>856100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>843800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>847400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>836400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>786400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>750400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>721500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>683800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>655100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>606500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>599100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>598800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>561800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>530200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>482500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>461400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>458800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>457300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>447100</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,85 +4184,89 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E57" s="3">
         <v>14500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>12100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>11900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>11500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>11000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>12400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>13100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>12600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>11300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>11700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4209,162 +4342,171 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>100300</v>
+      </c>
+      <c r="E59" s="3">
         <v>124700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>145300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>120000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>149900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>127100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>97800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>98200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>129400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>121800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>106200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>92500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>90600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>85600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>98500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>82700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>92300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>121100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>116100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>79500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>87900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>79000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>94600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>102400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>104200</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E60" s="3">
         <v>139200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>160700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>135100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>163400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>140400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>110200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>110300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>140200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>134400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>117800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>103200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>103800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>98500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>110400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>92300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>103800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>132100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>128500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>92600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>97100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>91600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>105900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>114100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>112700</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4440,85 +4582,91 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>54900</v>
+      </c>
+      <c r="E62" s="3">
         <v>57100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>60500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>66700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>68100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>52600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>53100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>55100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>57100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>56600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>55000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>58800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>61800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>63600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>66000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>69100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>64000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>64700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>52100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>57200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>30200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>30100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>30000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>30300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,85 +4902,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>165900</v>
+      </c>
+      <c r="E66" s="3">
         <v>196400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>221200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>201800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>231500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>193000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>163300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>165400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>197300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>191000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>172800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>162000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>165600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>162100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>176400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>161400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>167900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>196900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>180600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>149800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>127300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>121700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>135900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>144400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>150900</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5085,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,85 +5332,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>480600</v>
+      </c>
+      <c r="E72" s="3">
         <v>470800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>437000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>382300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>347800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>331900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>309800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>284100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>252000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>227500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>199700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>173100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>142300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>115300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>75300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>47200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>18100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-9400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-27700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-27100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-52900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-67000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-81900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-90600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-108100</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,85 +5652,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>841400</v>
+      </c>
+      <c r="E76" s="3">
         <v>829700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>792400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>761200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>725800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>706200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>692800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>678400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>650100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>645400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>613600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>588300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>555900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>521700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>478700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>445100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>431300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>401900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>381200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>380300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>355200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>339600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>322900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>313000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>296200</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E81" s="3">
         <v>41300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>54700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>34500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>16000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>22100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>25800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>32100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>24500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>27800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>26600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>30800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>27100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>39900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>28200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>29100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>27500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>18200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>24800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>14100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>14900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>8800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>17500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,43 +6009,44 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E83" s="3">
         <v>3900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>4900</v>
       </c>
       <c r="J83" s="3">
         <v>4900</v>
       </c>
       <c r="K83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="L83" s="3">
         <v>5000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>3900</v>
       </c>
       <c r="M83" s="3">
         <v>3900</v>
       </c>
       <c r="N83" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="O83" s="3">
         <v>4000</v>
@@ -5857,40 +6055,43 @@
         <v>4000</v>
       </c>
       <c r="Q83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="R83" s="3">
         <v>4200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2300</v>
-      </c>
-      <c r="U83" s="3">
-        <v>2200</v>
       </c>
       <c r="V83" s="3">
         <v>2200</v>
       </c>
       <c r="W83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="X83" s="3">
         <v>2300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2100</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>2600</v>
       </c>
       <c r="AA83" s="3">
         <v>2600</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,85 +6487,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E89" s="3">
         <v>32600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>61600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>40500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>52900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>32600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>22200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>46900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>61500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>38000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>44700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>42200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>28400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>60600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>48800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-12300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>32000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>40500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>12900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>38700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>11100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,85 +6599,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-1400</v>
       </c>
       <c r="Z91" s="3">
         <v>-1400</v>
       </c>
       <c r="AA91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,85 +6837,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-57300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-21400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-71000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-46100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-62700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-146900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>30000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>118600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-31700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-62600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-62000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-97900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>47000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-7000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-28200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-38400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>5300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,13 +6949,14 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-7200</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -6794,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,85 +7267,91 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-11700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-8800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-23300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-17600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1000</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>-2400</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7177,83 +7425,89 @@
         <v>0</v>
       </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-55100</v>
+      </c>
+      <c r="E102" s="3">
         <v>24100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>50700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-19600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-30400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-41700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-133500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>53600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>180300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-19700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>47600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-33400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>53600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-66800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>31300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>26000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>12300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>6400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>9000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>6100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PRDO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRDO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>PRDO</t>
   </si>
@@ -656,365 +656,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>168300</v>
+      </c>
+      <c r="E8" s="3">
         <v>147900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>179900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>186600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>195600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>176100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>168400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>167700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>183000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>159900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>174000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>175500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>183600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>171200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>169100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>176000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>171000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>158500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>155000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>156400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>157900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>145500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>145700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>142000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>148100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>143100</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E9" s="3">
         <v>30200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>33500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>32700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>33900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>31200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>30100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>27300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>28100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>25300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>26000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>28500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>29000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>28600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>27600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>28700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>26900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>24900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>25300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>25400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>26300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>25500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>27200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>30300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>26900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>138400</v>
+      </c>
+      <c r="E10" s="3">
         <v>117700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>146400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>153900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>161700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>144900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>138300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>140400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>154900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>134600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>148000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>147000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>154600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>142600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>141500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>147300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>144100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>133600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>129700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>131100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>131600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>120000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>118500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>111700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>121200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>114100</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,8 +1056,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1123,8 +1137,11 @@
       <c r="AB12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,38 +1220,41 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E14" s="3">
         <v>5500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>7400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2800</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1247,17 +1267,17 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>600</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
@@ -1268,11 +1288,11 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
+      <c r="X14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
@@ -1280,49 +1300,52 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E15" s="3">
         <v>3400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5100</v>
-      </c>
-      <c r="J15" s="3">
-        <v>4900</v>
       </c>
       <c r="K15" s="3">
         <v>4900</v>
       </c>
       <c r="L15" s="3">
+        <v>4900</v>
+      </c>
+      <c r="M15" s="3">
         <v>5000</v>
-      </c>
-      <c r="M15" s="3">
-        <v>3900</v>
       </c>
       <c r="N15" s="3">
         <v>3900</v>
       </c>
       <c r="O15" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="P15" s="3">
         <v>4000</v>
@@ -1331,40 +1354,43 @@
         <v>4000</v>
       </c>
       <c r="R15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="S15" s="3">
         <v>4200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2300</v>
-      </c>
-      <c r="V15" s="3">
-        <v>2200</v>
       </c>
       <c r="W15" s="3">
         <v>2200</v>
       </c>
       <c r="X15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Y15" s="3">
         <v>2300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2100</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>2600</v>
       </c>
       <c r="AB15" s="3">
         <v>2600</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>122000</v>
+      </c>
+      <c r="E17" s="3">
         <v>132000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>136900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>138500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>152300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>153500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>139100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>133700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>139300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>125300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>136100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>139600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>143000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>135000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>137100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>138700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>133700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>126400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>130700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>156300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>127900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>125300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>126400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>130700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>127500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>132400</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E18" s="3">
         <v>15900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>43100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>48100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>43300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>22600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>29300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>34000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>43700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>34600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>37900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>35900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>40600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>36200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>32000</v>
-      </c>
-      <c r="R18" s="3">
-        <v>37300</v>
       </c>
       <c r="S18" s="3">
         <v>37300</v>
       </c>
       <c r="T18" s="3">
+        <v>37300</v>
+      </c>
+      <c r="U18" s="3">
         <v>32100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>24300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>30000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>20200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>19300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>11300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>20600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,173 +1613,180 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E20" s="3">
         <v>6600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>26600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>900</v>
-      </c>
-      <c r="K20" s="3">
-        <v>200</v>
       </c>
       <c r="L20" s="3">
         <v>200</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>500</v>
-      </c>
-      <c r="P20" s="3">
-        <v>700</v>
       </c>
       <c r="Q20" s="3">
         <v>700</v>
       </c>
       <c r="R20" s="3">
+        <v>700</v>
+      </c>
+      <c r="S20" s="3">
         <v>1200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E21" s="3">
         <v>25900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>52100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>79100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>52300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>29400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>36500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>39700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>48800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>39700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>41800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>40200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>45100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>40900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>36800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>42700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>41400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>36000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>28400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>33900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>23700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>22600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>14000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>24100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>14100</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E22" s="3">
         <v>100</v>
@@ -1769,21 +1809,21 @@
       <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3" t="s">
+      <c r="L22" s="3">
+        <v>100</v>
+      </c>
+      <c r="M22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
@@ -1806,10 +1846,10 @@
         <v>0</v>
       </c>
       <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
         <v>400</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>100</v>
       </c>
       <c r="Z22" s="3">
         <v>100</v>
@@ -1820,168 +1860,177 @@
       <c r="AB22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>52900</v>
+      </c>
+      <c r="E23" s="3">
         <v>22400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>48100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>74600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>47100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>24400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>31300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>34700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>43800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>34800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>37300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>36000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>41000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>36900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>32800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>38500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>38700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>33600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>26000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>31600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>21000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>20200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>11800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>21400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E24" s="3">
         <v>5200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>19900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>12600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>9200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>8900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>11800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>10300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>9300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>10200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>9800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-7200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>10300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>9600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>6100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>6400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E26" s="3">
         <v>17200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>41300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>54700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>34500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>16000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>22100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>25800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>32100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>24500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>27800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>26700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>30800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>27100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>40000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>28200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>29100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>27500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>18400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>25200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>14000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>15100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>8900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>17900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E27" s="3">
         <v>17200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>41300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>54700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>34500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>16000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>22100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>25800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>32100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>24500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>27800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>26700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>30800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>27100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>40000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>28200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>29100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>27500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>18400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>25200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>14000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>15100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>8900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>17900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2329,8 +2390,8 @@
       <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2357,31 +2418,34 @@
         <v>0</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>-200</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>-400</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>100</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-200</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-100</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-400</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-52400</v>
       </c>
     </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,168 +2607,177 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-6600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-26600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-900</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-200</v>
       </c>
       <c r="L32" s="3">
         <v>-200</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-500</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-700</v>
       </c>
       <c r="Q32" s="3">
         <v>-700</v>
       </c>
       <c r="R32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="S32" s="3">
         <v>-1200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E33" s="3">
         <v>17200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>41300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>54700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>34500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>16000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>22100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>25800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>32100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>24500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>27800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>26600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>30800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>27100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>39900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>28200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>29100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>27500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>18200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>24800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>14100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>14900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>8800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>17500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E35" s="3">
         <v>17200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>41300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>54700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>34500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>16000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>22100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>25800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>32100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>24500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>27800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>26600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>30800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>27100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>39900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>28200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>29100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>27500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>18200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>24800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>14100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>14900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>8800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>17500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,283 +3091,293 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>125800</v>
+      </c>
+      <c r="E41" s="3">
         <v>118000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>165600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>140500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>411500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>109400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>147100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>148700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>190400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>320000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>266400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>87300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>86000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>105700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>58100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>91500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>37900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>108700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>47400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>51100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>38800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>32400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>32000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>33200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>24200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>515600</v>
+      </c>
+      <c r="E42" s="3">
         <v>485100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>429600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>428100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>99300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>399300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>375900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>366800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>307600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>174200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>209400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>389300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>361000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>300700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>305600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>250300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>243700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>185500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>234400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>228800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>200800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>196400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>156300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>151600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>158000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>156200</v>
       </c>
     </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>47200</v>
+      </c>
+      <c r="E43" s="3">
         <v>33900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>53300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>49200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>49300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>46000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>45300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>40800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>42900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>44700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>44400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>54300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>44200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>47600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>40300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>37100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>34100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>56400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>31200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>30500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>32400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>31300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>36500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>26900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>25300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E44" s="3">
         <v>5000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1200</v>
-      </c>
-      <c r="N44" s="3">
-        <v>600</v>
       </c>
       <c r="O44" s="3">
         <v>600</v>
@@ -3302,7 +3398,7 @@
         <v>600</v>
       </c>
       <c r="U44" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="V44" s="3">
         <v>700</v>
@@ -3311,202 +3407,211 @@
         <v>700</v>
       </c>
       <c r="X44" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y44" s="3">
         <v>800</v>
-      </c>
-      <c r="Y44" s="3">
-        <v>900</v>
       </c>
       <c r="Z44" s="3">
         <v>900</v>
       </c>
       <c r="AA44" s="3">
+        <v>900</v>
+      </c>
+      <c r="AB44" s="3">
         <v>1000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E45" s="3">
         <v>12900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>18900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>22700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>21600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>18500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>14200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>15800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>17600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>12200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>14600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>16000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>9200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>39300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>9800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>9500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>14400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>18100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>16900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>15300</v>
       </c>
     </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>706000</v>
+      </c>
+      <c r="E46" s="3">
         <v>655000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>669600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>643400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>585400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>575100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>582300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>571800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>556200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>554500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>537100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>549100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>506100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>467100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>416900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>394100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>332300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>360400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>353000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>320900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>282200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>269400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>240100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>230700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>225400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>210700</v>
       </c>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E47" s="3">
         <v>3900</v>
-      </c>
-      <c r="E47" s="3">
-        <v>1200</v>
       </c>
       <c r="F47" s="3">
         <v>1200</v>
       </c>
       <c r="G47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H47" s="3">
         <v>1500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1900</v>
-      </c>
-      <c r="I47" s="3">
-        <v>1300</v>
       </c>
       <c r="J47" s="3">
         <v>1300</v>
@@ -3515,191 +3620,197 @@
         <v>1300</v>
       </c>
       <c r="L47" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="M47" s="3">
         <v>1400</v>
       </c>
       <c r="N47" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O47" s="3">
         <v>1500</v>
-      </c>
-      <c r="O47" s="3">
-        <v>1300</v>
       </c>
       <c r="P47" s="3">
         <v>1300</v>
       </c>
       <c r="Q47" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="R47" s="3">
         <v>1200</v>
       </c>
       <c r="S47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="T47" s="3">
         <v>1100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E48" s="3">
         <v>40500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>45600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>47400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>50000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>52200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>56600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>59400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>62500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>65000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>64600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>65600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>68100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>72500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>75900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>77200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>79400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>76400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>78700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>67600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>71800</v>
-      </c>
-      <c r="X48" s="3">
-        <v>30000</v>
       </c>
       <c r="Y48" s="3">
         <v>30000</v>
       </c>
       <c r="Z48" s="3">
+        <v>30000</v>
+      </c>
+      <c r="AA48" s="3">
         <v>30800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>32000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>33200</v>
       </c>
     </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>276300</v>
+      </c>
+      <c r="E49" s="3">
         <v>277400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>281100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>293200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>294900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>297100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>228400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>191500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>193100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>194800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>196800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>132200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>133000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>133800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>134700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>135500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>137100</v>
-      </c>
-      <c r="T49" s="3">
-        <v>95300</v>
       </c>
       <c r="U49" s="3">
         <v>95300</v>
@@ -3725,8 +3836,11 @@
       <c r="AB49" s="3">
         <v>95300</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>95300</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,88 +4002,94 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E52" s="3">
         <v>30600</v>
-      </c>
-      <c r="E52" s="3">
-        <v>28500</v>
       </c>
       <c r="F52" s="3">
         <v>28500</v>
       </c>
       <c r="G52" s="3">
+        <v>28500</v>
+      </c>
+      <c r="H52" s="3">
         <v>31200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>31100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>30600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>32100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>30700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>31800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>36500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>38000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>41900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>46800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>55200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>47200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>56600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>65900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>70700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>77500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>80000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>86800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>93800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>99700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>101900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>105300</v>
       </c>
     </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,88 +4168,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1052000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1007300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1026000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1013700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>963000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>957400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>899200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>856100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>843800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>847400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>836400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>786400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>750400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>721500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>683800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>655100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>606500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>599100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>598800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>561800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>530200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>482500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>461400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>458800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>457300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>447100</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,88 +4315,92 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E57" s="3">
         <v>10800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>12400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>11500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>11900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>11500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>12400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>13100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>12600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>11300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>11700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4345,168 +4479,177 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>130700</v>
+      </c>
+      <c r="E59" s="3">
         <v>100300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>124700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>145300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>120000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>149900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>127100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>97800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>98200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>129400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>121800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>106200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>92500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>90600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>85600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>98500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>82700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>92300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>121100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>116100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>79500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>87900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>79000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>94600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>102400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>104200</v>
       </c>
     </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>142500</v>
+      </c>
+      <c r="E60" s="3">
         <v>111000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>139200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>160700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>135100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>163400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>140400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>110200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>110300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>140200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>134400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>117800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>103200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>103800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>98500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>110400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>92300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>103800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>132100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>128500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>92600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>97100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>91600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>105900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>114100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>112700</v>
       </c>
     </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4585,88 +4728,94 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>43400</v>
+      </c>
+      <c r="E62" s="3">
         <v>54900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>57100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>60500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>66700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>68100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>52600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>53100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>55100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>57100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>56600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>55000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>58800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>61800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>63600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>66000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>69100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>64000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>64700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>52100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>57200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>30200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>30100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>30000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>30300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,88 +5060,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>185900</v>
+      </c>
+      <c r="E66" s="3">
         <v>165900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>196400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>221200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>201800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>231500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>193000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>163300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>165400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>197300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>191000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>172800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>162000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>165600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>162100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>176400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>161400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>167900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>196900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>180600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>149800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>127300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>121700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>135900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>144400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>150900</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,88 +5506,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>512600</v>
+      </c>
+      <c r="E72" s="3">
         <v>480600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>470800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>437000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>382300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>347800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>331900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>309800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>284100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>252000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>227500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>199700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>173100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>142300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>115300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>75300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>47200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>18100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-9400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-27700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-27100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-52900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-67000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-81900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-90600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-108100</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,88 +5838,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>866100</v>
+      </c>
+      <c r="E76" s="3">
         <v>841400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>829700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>792400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>761200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>725800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>706200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>692800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>678400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>650100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>645400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>613600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>588300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>555900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>521700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>478700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>445100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>431300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>401900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>381200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>380300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>355200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>339600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>322900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>313000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>296200</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E81" s="3">
         <v>17200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>41300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>54700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>34500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>16000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>22100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>25800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>32100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>24500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>27800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>26600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>30800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>27100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>39900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>28200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>29100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>27500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>18200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>24800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>14100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>14900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>8800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>17500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,46 +6208,47 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E83" s="3">
         <v>3400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>4900</v>
       </c>
       <c r="K83" s="3">
         <v>4900</v>
       </c>
       <c r="L83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="M83" s="3">
         <v>5000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>3900</v>
       </c>
       <c r="N83" s="3">
         <v>3900</v>
       </c>
       <c r="O83" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="P83" s="3">
         <v>4000</v>
@@ -6058,40 +6257,43 @@
         <v>4000</v>
       </c>
       <c r="R83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="S83" s="3">
         <v>4200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2300</v>
-      </c>
-      <c r="V83" s="3">
-        <v>2200</v>
       </c>
       <c r="W83" s="3">
         <v>2200</v>
       </c>
       <c r="X83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Y83" s="3">
         <v>2300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2100</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>2600</v>
       </c>
       <c r="AB83" s="3">
         <v>2600</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,88 +6704,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>54500</v>
+      </c>
+      <c r="E89" s="3">
         <v>13200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>32600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>61600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>40500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>52900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>32600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>22200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>46900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>61500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>38000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>44700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>42200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>28400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>60600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>48800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-12300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>32000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>40500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>12900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>38700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>11100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,88 +6820,92 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-1400</v>
       </c>
       <c r="AA91" s="3">
         <v>-1400</v>
       </c>
       <c r="AB91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,88 +7067,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-30800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-57300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-21400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-71000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-46100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-62700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-146900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>30000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>118600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-31700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-62600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-62000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-97900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>47000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-7000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-28200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-38400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>5300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,17 +7183,18 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>-7200</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,88 +7513,94 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-11000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-11700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-8800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-23300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-17600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1000</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>-2400</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7428,86 +7677,92 @@
         <v>0</v>
       </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-55100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>24100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>50700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-19600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-30400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-41700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-133500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>53600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>180300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-19700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>47600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-33400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>53600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-66800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>31300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>26000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>12300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>6400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>9000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>6100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PRDO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRDO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>PRDO</t>
   </si>
@@ -656,378 +656,391 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>166700</v>
+      </c>
+      <c r="E8" s="3">
         <v>168300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>147900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>179900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>186600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>195600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>176100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>168400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>167700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>183000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>159900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>174000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>175500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>183600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>171200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>169100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>176000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>171000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>158500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>155000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>156400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>157900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>145500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>145700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>142000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>148100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>143100</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E9" s="3">
         <v>29900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>30200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>33500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>32700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>33900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>31200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>30100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>27300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>28100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>25300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>26000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>28500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>29000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>28600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>27600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>28700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>26900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>24900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>25300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>25400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>26300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>25500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>27200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>30300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>26900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>139200</v>
+      </c>
+      <c r="E10" s="3">
         <v>138400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>117700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>146400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>153900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>161700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>144900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>138300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>140400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>154900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>134600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>148000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>147000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>154600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>142600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>141500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>147300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>144100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>133600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>129700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>131100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>131600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>120000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>118500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>111700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>121200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>114100</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1057,8 +1070,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1140,8 +1154,11 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,41 +1240,44 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>800</v>
+      </c>
+      <c r="E14" s="3">
         <v>1600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>5500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>7400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2800</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1270,17 +1290,17 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>600</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
@@ -1291,11 +1311,11 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
@@ -1303,52 +1323,55 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E15" s="3">
         <v>3000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5100</v>
-      </c>
-      <c r="K15" s="3">
-        <v>4900</v>
       </c>
       <c r="L15" s="3">
         <v>4900</v>
       </c>
       <c r="M15" s="3">
+        <v>4900</v>
+      </c>
+      <c r="N15" s="3">
         <v>5000</v>
-      </c>
-      <c r="N15" s="3">
-        <v>3900</v>
       </c>
       <c r="O15" s="3">
         <v>3900</v>
       </c>
       <c r="P15" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="Q15" s="3">
         <v>4000</v>
@@ -1357,40 +1380,43 @@
         <v>4000</v>
       </c>
       <c r="S15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="T15" s="3">
         <v>4200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2300</v>
-      </c>
-      <c r="W15" s="3">
-        <v>2200</v>
       </c>
       <c r="X15" s="3">
         <v>2200</v>
       </c>
       <c r="Y15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Z15" s="3">
         <v>2300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2100</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>2600</v>
       </c>
       <c r="AC15" s="3">
         <v>2600</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1443,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>120700</v>
+      </c>
+      <c r="E17" s="3">
         <v>122000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>132000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>136900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>138500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>152300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>153500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>139100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>133700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>139300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>125300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>136100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>139600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>143000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>135000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>137100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>138700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>133700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>126400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>130700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>156300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>127900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>125300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>126400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>130700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>127500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>132400</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E18" s="3">
         <v>46300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>15900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>43100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>48100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>43300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>22600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>29300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>34000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>43700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>34600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>37900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>35900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>40600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>36200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>32000</v>
-      </c>
-      <c r="S18" s="3">
-        <v>37300</v>
       </c>
       <c r="T18" s="3">
         <v>37300</v>
       </c>
       <c r="U18" s="3">
+        <v>37300</v>
+      </c>
+      <c r="V18" s="3">
         <v>32100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>24300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>30000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>20200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>19300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>11300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>20600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,91 +1647,95 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E20" s="3">
         <v>6900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>6600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>26600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>900</v>
-      </c>
-      <c r="L20" s="3">
-        <v>200</v>
       </c>
       <c r="M20" s="3">
         <v>200</v>
       </c>
       <c r="N20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>500</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>700</v>
       </c>
       <c r="R20" s="3">
         <v>700</v>
       </c>
       <c r="S20" s="3">
+        <v>700</v>
+      </c>
+      <c r="T20" s="3">
         <v>1200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1706,90 +1743,93 @@
         <v>56200</v>
       </c>
       <c r="E21" s="3">
+        <v>56200</v>
+      </c>
+      <c r="F21" s="3">
         <v>25900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>52100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>79100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>52300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>29400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>36500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>39700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>48800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>39700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>41800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>40200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>45100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>40900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>36800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>42700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>41400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>36000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>28400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>33900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>23700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>22600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>14000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>24100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>14100</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>100</v>
+      </c>
+      <c r="E22" s="3">
         <v>300</v>
-      </c>
-      <c r="E22" s="3">
-        <v>100</v>
       </c>
       <c r="F22" s="3">
         <v>100</v>
@@ -1812,21 +1852,21 @@
       <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3" t="s">
+      <c r="M22" s="3">
+        <v>100</v>
+      </c>
+      <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -1849,10 +1889,10 @@
         <v>0</v>
       </c>
       <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
         <v>400</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>100</v>
       </c>
       <c r="AA22" s="3">
         <v>100</v>
@@ -1863,174 +1903,183 @@
       <c r="AC22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E23" s="3">
         <v>52900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>22400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>48100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>74600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>47100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>24400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>31300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>34700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>43800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>34800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>37300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>36000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>41000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>36900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>32800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>38500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>38700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>33600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>26000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>31600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>21000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>20200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>11800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>21400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E24" s="3">
         <v>13400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>19900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>12600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>9200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>8900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>11800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>10300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>9600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>10200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-7200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>10300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>9600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>7700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2161,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E26" s="3">
         <v>39400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>17200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>41300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>54700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>34500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>16000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>22100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>25800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>32100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>24500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>27800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>26700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>30800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>27100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>40000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>28200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>29100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>27500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>18400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>25200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>14000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>15100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>8900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>17900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E27" s="3">
         <v>39400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>17200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>41300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>54700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>34500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>16000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>22100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>25800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>32100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>24500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>27800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>26700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>30800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>27100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>40000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>28200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>29100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>27500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>18400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>25200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>14000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>15100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>8900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>17900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2393,8 +2454,8 @@
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -2421,31 +2482,34 @@
         <v>0</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>-200</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-400</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>100</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-200</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-100</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-400</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-52400</v>
       </c>
     </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,174 +2677,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-6900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-6600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-26600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-900</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-200</v>
       </c>
       <c r="M32" s="3">
         <v>-200</v>
       </c>
       <c r="N32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-500</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-700</v>
       </c>
       <c r="R32" s="3">
         <v>-700</v>
       </c>
       <c r="S32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="T32" s="3">
         <v>-1200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E33" s="3">
         <v>39400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>17200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>41300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>54700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>34500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>16000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>22100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>25800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>32100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>24500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>27800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>26600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>30800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>27100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>39900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>28200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>29100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>27500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>18200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>24800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>14100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>14900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>8800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>17500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E35" s="3">
         <v>39400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>17200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>41300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>54700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>34500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>16000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>22100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>25800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>32100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>24500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>27800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>26600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>30800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>27100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>39900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>28200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>29100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>27500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>18200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>24800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>14100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>14900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>8800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>17500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,295 +3178,305 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>127900</v>
+      </c>
+      <c r="E41" s="3">
         <v>125800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>118000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>165600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>140500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>411500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>109400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>147100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>148700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>190400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>320000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>266400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>87300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>86000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>105700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>58100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>91500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>37900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>108700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>47400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>51100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>38800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>32400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>32000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>33200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>24200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>546300</v>
+      </c>
+      <c r="E42" s="3">
         <v>515600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>485100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>429600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>428100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>99300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>399300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>375900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>366800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>307600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>174200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>209400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>389300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>361000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>300700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>305600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>250300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>243700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>185500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>234400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>228800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>200800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>196400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>156300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>151600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>158000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>156200</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>39800</v>
+      </c>
+      <c r="E43" s="3">
         <v>47200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>33900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>53300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>49200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>49300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>46000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>45300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>40800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>42900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>44700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>44400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>54300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>44200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>47600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>40300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>37100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>34100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>56400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>31200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>30500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>32400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>31300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>36500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>26900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>25300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E44" s="3">
         <v>4300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1200</v>
-      </c>
-      <c r="O44" s="3">
-        <v>600</v>
       </c>
       <c r="P44" s="3">
         <v>600</v>
@@ -3401,7 +3497,7 @@
         <v>600</v>
       </c>
       <c r="V44" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="W44" s="3">
         <v>700</v>
@@ -3410,211 +3506,220 @@
         <v>700</v>
       </c>
       <c r="Y44" s="3">
+        <v>700</v>
+      </c>
+      <c r="Z44" s="3">
         <v>800</v>
-      </c>
-      <c r="Z44" s="3">
-        <v>900</v>
       </c>
       <c r="AA44" s="3">
         <v>900</v>
       </c>
       <c r="AB44" s="3">
+        <v>900</v>
+      </c>
+      <c r="AC44" s="3">
         <v>1000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E45" s="3">
         <v>13100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>18900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>22700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>21600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>18500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>12000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>15800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>17600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>14300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>12600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>14600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>16000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>9200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>39300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>9800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>9500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>8500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>14400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>18100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>16900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>15300</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>732500</v>
+      </c>
+      <c r="E46" s="3">
         <v>706000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>655000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>669600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>643400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>585400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>575100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>582300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>571800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>556200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>554500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>537100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>549100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>506100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>467100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>416900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>394100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>332300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>360400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>353000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>320900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>282200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>269400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>240100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>230700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>225400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>210700</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E47" s="3">
         <v>4900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3900</v>
-      </c>
-      <c r="F47" s="3">
-        <v>1200</v>
       </c>
       <c r="G47" s="3">
         <v>1200</v>
       </c>
       <c r="H47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I47" s="3">
         <v>1500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1900</v>
-      </c>
-      <c r="J47" s="3">
-        <v>1300</v>
       </c>
       <c r="K47" s="3">
         <v>1300</v>
@@ -3623,197 +3728,203 @@
         <v>1300</v>
       </c>
       <c r="M47" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="N47" s="3">
         <v>1400</v>
       </c>
       <c r="O47" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P47" s="3">
         <v>1500</v>
-      </c>
-      <c r="P47" s="3">
-        <v>1300</v>
       </c>
       <c r="Q47" s="3">
         <v>1300</v>
       </c>
       <c r="R47" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="S47" s="3">
         <v>1200</v>
       </c>
       <c r="T47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="U47" s="3">
         <v>1100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E48" s="3">
         <v>34900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>40500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>45600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>47400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>50000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>52200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>56600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>59400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>62500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>65000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>64600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>65600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>68100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>72500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>75900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>77200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>79400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>76400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>78700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>67600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>71800</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>30000</v>
       </c>
       <c r="Z48" s="3">
         <v>30000</v>
       </c>
       <c r="AA48" s="3">
+        <v>30000</v>
+      </c>
+      <c r="AB48" s="3">
         <v>30800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>32000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>33200</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>275200</v>
+      </c>
+      <c r="E49" s="3">
         <v>276300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>277400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>281100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>293200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>294900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>297100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>228400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>191500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>193100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>194800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>196800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>132200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>133000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>133800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>134700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>135500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>137100</v>
-      </c>
-      <c r="U49" s="3">
-        <v>95300</v>
       </c>
       <c r="V49" s="3">
         <v>95300</v>
@@ -3839,8 +3950,11 @@
       <c r="AC49" s="3">
         <v>95300</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>95300</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,91 +4122,97 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E52" s="3">
         <v>29900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>30600</v>
-      </c>
-      <c r="F52" s="3">
-        <v>28500</v>
       </c>
       <c r="G52" s="3">
         <v>28500</v>
       </c>
       <c r="H52" s="3">
+        <v>28500</v>
+      </c>
+      <c r="I52" s="3">
         <v>31200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>31100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>30600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>32100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>30700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>31800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>36500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>38000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>41900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>46800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>55200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>47200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>56600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>65900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>70700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>77500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>80000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>86800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>93800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>99700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>101900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>105300</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,91 +4294,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1078200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1052000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1007300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1026000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1013700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>963000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>957400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>899200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>856100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>843800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>847400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>836400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>786400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>750400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>721500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>683800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>655100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>606500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>599100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>598800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>561800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>530200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>482500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>461400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>458800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>457300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>447100</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,91 +4446,95 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E57" s="3">
         <v>11800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>13300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>11900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>11000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>12400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>13100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>9200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>12600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>11300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>11700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4482,174 +4616,183 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>121600</v>
+      </c>
+      <c r="E59" s="3">
         <v>130700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>100300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>124700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>145300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>120000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>149900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>127100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>97800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>98200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>129400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>121800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>106200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>92500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>90600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>85600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>98500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>82700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>92300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>121100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>116100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>79500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>87900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>79000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>94600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>102400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>104200</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>134900</v>
+      </c>
+      <c r="E60" s="3">
         <v>142500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>111000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>139200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>160700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>135100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>163400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>140400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>110200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>110300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>140200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>134400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>117800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>103200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>103800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>98500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>110400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>92300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>103800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>132100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>128500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>92600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>97100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>91600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>105900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>114100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>112700</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4731,91 +4874,97 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E62" s="3">
         <v>43400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>54900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>57100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>60500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>66700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>68100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>52600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>53100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>55100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>57100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>56600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>55000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>58800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>61800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>63600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>66000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>69100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>64000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>64700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>52100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>57200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>30200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>30100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>30000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>30300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,91 +5218,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>178700</v>
+      </c>
+      <c r="E66" s="3">
         <v>185900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>165900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>196400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>221200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>201800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>231500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>193000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>163300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>165400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>197300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>191000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>172800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>162000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>165600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>162100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>176400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>161400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>167900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>196900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>180600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>149800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>127300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>121700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>135900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>144400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>150900</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,91 +5680,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>543600</v>
+      </c>
+      <c r="E72" s="3">
         <v>512600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>480600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>470800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>437000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>382300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>347800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>331900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>309800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>284100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>252000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>227500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>199700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>173100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>142300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>115300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>75300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>47200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>18100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-9400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-27700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-27100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-52900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-67000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-81900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-90600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-108100</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,91 +6024,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>899500</v>
+      </c>
+      <c r="E76" s="3">
         <v>866100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>841400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>829700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>792400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>761200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>725800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>706200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>692800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>678400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>650100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>645400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>613600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>588300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>555900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>521700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>478700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>445100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>431300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>401900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>381200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>380300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>355200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>339600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>322900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>313000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>296200</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E81" s="3">
         <v>39400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>17200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>41300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>54700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>34500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>16000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>22100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>25800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>32100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>24500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>27800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>26600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>30800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>27100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>39900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>28200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>29100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>27500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>18200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>24800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>14100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>14900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>8800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>17500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,49 +6407,50 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E83" s="3">
         <v>3000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>4900</v>
       </c>
       <c r="L83" s="3">
         <v>4900</v>
       </c>
       <c r="M83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="N83" s="3">
         <v>5000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>3900</v>
       </c>
       <c r="O83" s="3">
         <v>3900</v>
       </c>
       <c r="P83" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="Q83" s="3">
         <v>4000</v>
@@ -6260,40 +6459,43 @@
         <v>4000</v>
       </c>
       <c r="S83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="T83" s="3">
         <v>4200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2300</v>
-      </c>
-      <c r="W83" s="3">
-        <v>2200</v>
       </c>
       <c r="X83" s="3">
         <v>2200</v>
       </c>
       <c r="Y83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Z83" s="3">
         <v>2300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2100</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>2600</v>
       </c>
       <c r="AC83" s="3">
         <v>2600</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +6921,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E89" s="3">
         <v>54500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>32600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>61600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>40500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>52900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>32600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>22200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>46900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>61500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>38000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>44700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>42200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>28400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>60600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>48800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-12300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>32000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>40500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>12900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>38700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>11100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,91 +7041,95 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-1400</v>
       </c>
       <c r="AB91" s="3">
         <v>-1400</v>
       </c>
       <c r="AC91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,91 +7297,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-29300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-30800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-57300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-21400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-71000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-46100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-62700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-146900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>30000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>118600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-31700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-62600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-62000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-7600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-97900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>47000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-7000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-28200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-38400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>5300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,19 +7417,20 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-7400</v>
       </c>
       <c r="E96" s="3">
         <v>-7200</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-7200</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,91 +7759,97 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-15900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-11000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-11700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-8800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-23300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-17600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1000</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7680,89 +7929,95 @@
         <v>0</v>
       </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E102" s="3">
         <v>7800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-55100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>24100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>50700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-19600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-30400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-41700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-133500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>53600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>180300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-19700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>47600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-33400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>53600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-66800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>31300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>26000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>12300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>6400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>9000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>6100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PRDO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRDO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
   <si>
     <t>PRDO</t>
   </si>
@@ -656,391 +656,404 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>169800</v>
+      </c>
+      <c r="E8" s="3">
         <v>166700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>168300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>147900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>179900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>186600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>195600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>176100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>168400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>167700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>183000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>159900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>174000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>175500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>183600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>171200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>169100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>176000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>171000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>158500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>155000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>156400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>157900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>145500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>145700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>142000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>148100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>143100</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>27500</v>
+        <v>26600</v>
       </c>
       <c r="E9" s="3">
-        <v>29900</v>
+        <v>26100</v>
       </c>
       <c r="F9" s="3">
+        <v>27600</v>
+      </c>
+      <c r="G9" s="3">
+        <v>27700</v>
+      </c>
+      <c r="H9" s="3">
+        <v>31000</v>
+      </c>
+      <c r="I9" s="3">
         <v>30200</v>
       </c>
-      <c r="G9" s="3">
-        <v>33500</v>
-      </c>
-      <c r="H9" s="3">
-        <v>32700</v>
-      </c>
-      <c r="I9" s="3">
-        <v>33900</v>
-      </c>
       <c r="J9" s="3">
+        <v>31100</v>
+      </c>
+      <c r="K9" s="3">
         <v>31200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>30100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>27300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>28100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>25300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>26000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>28500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>29000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>28600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>27600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>28700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>26900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>24900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>25300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>25400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>26300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>25500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>27200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>30300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>26900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>139200</v>
+        <v>143200</v>
       </c>
       <c r="E10" s="3">
-        <v>138400</v>
+        <v>140700</v>
       </c>
       <c r="F10" s="3">
-        <v>117700</v>
+        <v>140700</v>
       </c>
       <c r="G10" s="3">
-        <v>146400</v>
+        <v>120200</v>
       </c>
       <c r="H10" s="3">
-        <v>153900</v>
+        <v>148900</v>
       </c>
       <c r="I10" s="3">
-        <v>161700</v>
+        <v>156300</v>
       </c>
       <c r="J10" s="3">
+        <v>164500</v>
+      </c>
+      <c r="K10" s="3">
         <v>144900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>138300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>140400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>154900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>134600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>148000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>147000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>154600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>142600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>141500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>147300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>144100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>133600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>129700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>131100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>131600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>120000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>118500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>111700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>121200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>114100</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1071,8 +1084,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1157,8 +1171,11 @@
       <c r="AD12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1243,44 +1260,47 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1600</v>
       </c>
-      <c r="F14" s="3">
-        <v>5500</v>
-      </c>
       <c r="G14" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="H14" s="3">
         <v>7400</v>
       </c>
-      <c r="H14" s="3">
-        <v>800</v>
-      </c>
       <c r="I14" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="J14" s="3">
         <v>600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2800</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
@@ -1293,17 +1313,17 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>600</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1314,11 +1334,11 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
+      <c r="Z14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
@@ -1326,11 +1346,14 @@
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1338,43 +1361,43 @@
         <v>3100</v>
       </c>
       <c r="E15" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F15" s="3">
         <v>3000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5100</v>
-      </c>
-      <c r="L15" s="3">
-        <v>4900</v>
       </c>
       <c r="M15" s="3">
         <v>4900</v>
       </c>
       <c r="N15" s="3">
+        <v>4900</v>
+      </c>
+      <c r="O15" s="3">
         <v>5000</v>
-      </c>
-      <c r="O15" s="3">
-        <v>3900</v>
       </c>
       <c r="P15" s="3">
         <v>3900</v>
       </c>
       <c r="Q15" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="R15" s="3">
         <v>4000</v>
@@ -1383,40 +1406,43 @@
         <v>4000</v>
       </c>
       <c r="T15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="U15" s="3">
         <v>4200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2300</v>
-      </c>
-      <c r="X15" s="3">
-        <v>2200</v>
       </c>
       <c r="Y15" s="3">
         <v>2200</v>
       </c>
       <c r="Z15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AA15" s="3">
         <v>2300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>2100</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>2600</v>
       </c>
       <c r="AD15" s="3">
         <v>2600</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1470,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>120700</v>
+        <v>125000</v>
       </c>
       <c r="E17" s="3">
-        <v>122000</v>
+        <v>119900</v>
       </c>
       <c r="F17" s="3">
-        <v>132000</v>
+        <v>120400</v>
       </c>
       <c r="G17" s="3">
-        <v>136900</v>
+        <v>126400</v>
       </c>
       <c r="H17" s="3">
-        <v>138500</v>
+        <v>129500</v>
       </c>
       <c r="I17" s="3">
-        <v>152300</v>
+        <v>137700</v>
       </c>
       <c r="J17" s="3">
+        <v>151700</v>
+      </c>
+      <c r="K17" s="3">
         <v>153500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>139100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>133700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>139300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>125300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>136100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>139600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>143000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>135000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>137100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>138700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>133700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>126400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>130700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>156300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>127900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>125300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>126400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>130700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>127500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>132400</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>46000</v>
+        <v>44800</v>
       </c>
       <c r="E18" s="3">
-        <v>46300</v>
+        <v>46800</v>
       </c>
       <c r="F18" s="3">
-        <v>15900</v>
+        <v>47900</v>
       </c>
       <c r="G18" s="3">
-        <v>43100</v>
+        <v>21500</v>
       </c>
       <c r="H18" s="3">
-        <v>48100</v>
+        <v>50500</v>
       </c>
       <c r="I18" s="3">
-        <v>43300</v>
+        <v>48900</v>
       </c>
       <c r="J18" s="3">
+        <v>43900</v>
+      </c>
+      <c r="K18" s="3">
         <v>22600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>29300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>34000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>43700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>34600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>37900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>35900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>40600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>36200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>32000</v>
-      </c>
-      <c r="T18" s="3">
-        <v>37300</v>
       </c>
       <c r="U18" s="3">
         <v>37300</v>
       </c>
       <c r="V18" s="3">
+        <v>37300</v>
+      </c>
+      <c r="W18" s="3">
         <v>32100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>24300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>30000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>20200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>19300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>11300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>20600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,180 +1681,187 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>7200</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>6900</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
-        <v>6600</v>
+        <v>-100</v>
       </c>
       <c r="G20" s="3">
-        <v>5100</v>
+        <v>22000</v>
       </c>
       <c r="H20" s="3">
-        <v>26600</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3">
-        <v>3800</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>1900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>900</v>
-      </c>
-      <c r="M20" s="3">
-        <v>200</v>
       </c>
       <c r="N20" s="3">
         <v>200</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>500</v>
-      </c>
-      <c r="R20" s="3">
-        <v>700</v>
       </c>
       <c r="S20" s="3">
         <v>700</v>
       </c>
       <c r="T20" s="3">
+        <v>700</v>
+      </c>
+      <c r="U20" s="3">
         <v>1200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>56200</v>
+        <v>47800</v>
       </c>
       <c r="E21" s="3">
-        <v>56200</v>
+        <v>49800</v>
       </c>
       <c r="F21" s="3">
-        <v>25900</v>
+        <v>51000</v>
       </c>
       <c r="G21" s="3">
-        <v>52100</v>
+        <v>3000</v>
       </c>
       <c r="H21" s="3">
-        <v>79100</v>
+        <v>54300</v>
       </c>
       <c r="I21" s="3">
-        <v>52300</v>
+        <v>53200</v>
       </c>
       <c r="J21" s="3">
+        <v>49100</v>
+      </c>
+      <c r="K21" s="3">
         <v>29400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>36500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>39700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>48800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>39700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>41800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>40200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>45100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>40900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>36800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>42700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>41400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>36000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>28400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>33900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>23700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>22600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>14000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>24100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>14100</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1829,10 +1869,10 @@
         <v>100</v>
       </c>
       <c r="E22" s="3">
+        <v>100</v>
+      </c>
+      <c r="F22" s="3">
         <v>300</v>
-      </c>
-      <c r="F22" s="3">
-        <v>100</v>
       </c>
       <c r="G22" s="3">
         <v>100</v>
@@ -1855,21 +1895,21 @@
       <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3" t="s">
+      <c r="N22" s="3">
+        <v>100</v>
+      </c>
+      <c r="O22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
@@ -1892,10 +1932,10 @@
         <v>0</v>
       </c>
       <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
         <v>400</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>100</v>
       </c>
       <c r="AB22" s="3">
         <v>100</v>
@@ -1906,180 +1946,189 @@
       <c r="AD22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>52400</v>
+      </c>
+      <c r="E23" s="3">
         <v>53000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>52900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>22400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>48100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>74600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>47100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>24400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>31300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>34700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>43800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>34800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>37300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>36000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>41000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>36900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>32800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>38500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>38700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>33600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>26000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>31600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>21000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>20200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>11800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>21400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E24" s="3">
         <v>14600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>13400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>19900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>12600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>8500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>8900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>11800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>10300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>9300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>10200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>9800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-7200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>10300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>9600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2213,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E26" s="3">
         <v>38400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>39400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>17200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>41300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>54700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>34500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>16000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>22100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>25800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>32100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>24500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>27800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>26700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>30800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>27100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>40000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>28200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>29100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>27500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>18400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>25200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>14000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>15100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>8900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>17900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E27" s="3">
         <v>38400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>39400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>17200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>41300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>54700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>34500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>16000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>22100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>25800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>32100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>24500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>27800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>26700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>30800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>27100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>40000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>28200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>29100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>27500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>18400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>25200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>14000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>15100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>8900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>17900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,31 +2480,34 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -2457,8 +2518,8 @@
       <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -2485,31 +2546,34 @@
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>-200</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-400</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>100</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-200</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-100</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-400</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-52400</v>
       </c>
     </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2658,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,180 +2747,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-7200</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>-6900</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
-        <v>-6600</v>
+        <v>100</v>
       </c>
       <c r="G32" s="3">
-        <v>-5100</v>
+        <v>-22000</v>
       </c>
       <c r="H32" s="3">
-        <v>-26600</v>
+        <v>-100</v>
       </c>
       <c r="I32" s="3">
-        <v>-3800</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-900</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-200</v>
       </c>
       <c r="N32" s="3">
         <v>-200</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-500</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-700</v>
       </c>
       <c r="S32" s="3">
         <v>-700</v>
       </c>
       <c r="T32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="U32" s="3">
         <v>-1200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E33" s="3">
         <v>38400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>39400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>17200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>41300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>54700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>34500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>16000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>22100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>25800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>32100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>24500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>27800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>26600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>30800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>27100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>39900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>28200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>29100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>27500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>18200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>24800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>14100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>14900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>8800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>17500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3014,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E35" s="3">
         <v>38400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>39400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>17200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>41300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>54700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>34500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>16000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>22100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>25800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>32100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>24500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>27800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>26600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>30800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>27100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>39900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>28200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>29100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>27500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>18200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>24800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>14100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>14900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>8800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>17500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3232,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,307 +3265,317 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>238000</v>
+      </c>
+      <c r="E41" s="3">
         <v>127900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>125800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>118000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>165600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>140500</v>
       </c>
-      <c r="I41" s="3">
-        <v>411500</v>
-      </c>
       <c r="J41" s="3">
+        <v>89800</v>
+      </c>
+      <c r="K41" s="3">
         <v>109400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>147100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>148700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>190400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>320000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>266400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>87300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>86000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>105700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>58100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>91500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>37900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>108700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>47400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>51100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>38800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>32400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>32000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>33200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>24200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>483800</v>
+      </c>
+      <c r="E42" s="3">
         <v>546300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>515600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>485100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>429600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>428100</v>
       </c>
-      <c r="I42" s="3">
-        <v>99300</v>
-      </c>
       <c r="J42" s="3">
+        <v>420900</v>
+      </c>
+      <c r="K42" s="3">
         <v>399300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>375900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>366800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>307600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>174200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>209400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>389300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>361000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>300700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>305600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>250300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>243700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>185500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>234400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>228800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>200800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>196400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>156300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>151600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>158000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>156200</v>
       </c>
     </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E43" s="3">
         <v>39800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>47200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>33900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>53300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>49200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>49300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>46000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>45300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>40800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>42900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>44700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>44400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>54300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>44200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>47600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>40300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>37100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>34100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>56400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>31200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>30500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>32400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>31300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>36500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>26900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>25300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E44" s="3">
         <v>4500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1200</v>
-      </c>
-      <c r="P44" s="3">
-        <v>600</v>
       </c>
       <c r="Q44" s="3">
         <v>600</v>
@@ -3500,7 +3596,7 @@
         <v>600</v>
       </c>
       <c r="W44" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="X44" s="3">
         <v>700</v>
@@ -3509,220 +3605,229 @@
         <v>700</v>
       </c>
       <c r="Z44" s="3">
+        <v>700</v>
+      </c>
+      <c r="AA44" s="3">
         <v>800</v>
-      </c>
-      <c r="AA44" s="3">
-        <v>900</v>
       </c>
       <c r="AB44" s="3">
         <v>900</v>
       </c>
       <c r="AC44" s="3">
+        <v>900</v>
+      </c>
+      <c r="AD44" s="3">
         <v>1000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>14100</v>
+        <v>300</v>
       </c>
       <c r="E45" s="3">
-        <v>13100</v>
+        <v>500</v>
       </c>
       <c r="F45" s="3">
-        <v>12900</v>
+        <v>200</v>
       </c>
       <c r="G45" s="3">
-        <v>18900</v>
+        <v>200</v>
       </c>
       <c r="H45" s="3">
-        <v>22700</v>
+        <v>300</v>
       </c>
       <c r="I45" s="3">
-        <v>21600</v>
+        <v>700</v>
       </c>
       <c r="J45" s="3">
+        <v>700</v>
+      </c>
+      <c r="K45" s="3">
         <v>18500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>12000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>15800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>17600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>14300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>12200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>14600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>16000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>9200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>39300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>9800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>9500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>8500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>14400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>18100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>16900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>15300</v>
       </c>
     </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>773500</v>
+      </c>
+      <c r="E46" s="3">
         <v>732500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>706000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>655000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>669600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>643400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>585400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>575100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>582300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>571800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>556200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>554500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>537100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>549100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>506100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>467100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>416900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>394100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>332300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>360400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>353000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>320900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>282200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>269400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>240100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>230700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>225400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>210700</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>5300</v>
+        <v>1200</v>
       </c>
       <c r="E47" s="3">
-        <v>4900</v>
-      </c>
-      <c r="F47" s="3">
-        <v>3900</v>
+        <v>1200</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G47" s="3">
         <v>1200</v>
       </c>
       <c r="H47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I47" s="3">
         <v>1200</v>
       </c>
-      <c r="I47" s="3">
-        <v>1500</v>
-      </c>
       <c r="J47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K47" s="3">
         <v>1900</v>
-      </c>
-      <c r="K47" s="3">
-        <v>1300</v>
       </c>
       <c r="L47" s="3">
         <v>1300</v>
@@ -3731,203 +3836,209 @@
         <v>1300</v>
       </c>
       <c r="N47" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="O47" s="3">
         <v>1400</v>
       </c>
       <c r="P47" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q47" s="3">
         <v>1500</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>1300</v>
       </c>
       <c r="R47" s="3">
         <v>1300</v>
       </c>
       <c r="S47" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="T47" s="3">
         <v>1200</v>
       </c>
       <c r="U47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="V47" s="3">
         <v>1100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E48" s="3">
         <v>35500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>34900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>40500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>45600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>47400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>50000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>52200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>56600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>59400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>62500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>65000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>64600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>65600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>68100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>72500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>75900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>77200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>79400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>76400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>78700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>67600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>71800</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>30000</v>
       </c>
       <c r="AA48" s="3">
         <v>30000</v>
       </c>
       <c r="AB48" s="3">
+        <v>30000</v>
+      </c>
+      <c r="AC48" s="3">
         <v>30800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>32000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>33200</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>274100</v>
+      </c>
+      <c r="E49" s="3">
         <v>275200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>276300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>277400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>281100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>293200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>294900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>297100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>228400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>191500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>193100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>194800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>196800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>132200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>133000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>133800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>134700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>135500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>137100</v>
-      </c>
-      <c r="V49" s="3">
-        <v>95300</v>
       </c>
       <c r="W49" s="3">
         <v>95300</v>
@@ -3953,8 +4064,11 @@
       <c r="AD49" s="3">
         <v>95300</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>95300</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4153,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,94 +4242,100 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>29800</v>
+        <v>5300</v>
       </c>
       <c r="E52" s="3">
-        <v>29900</v>
+        <v>5300</v>
       </c>
       <c r="F52" s="3">
+        <v>6800</v>
+      </c>
+      <c r="G52" s="3">
+        <v>5600</v>
+      </c>
+      <c r="H52" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I52" s="3">
+        <v>5700</v>
+      </c>
+      <c r="J52" s="3">
+        <v>5700</v>
+      </c>
+      <c r="K52" s="3">
+        <v>31100</v>
+      </c>
+      <c r="L52" s="3">
         <v>30600</v>
       </c>
-      <c r="G52" s="3">
-        <v>28500</v>
-      </c>
-      <c r="H52" s="3">
-        <v>28500</v>
-      </c>
-      <c r="I52" s="3">
-        <v>31200</v>
-      </c>
-      <c r="J52" s="3">
-        <v>31100</v>
-      </c>
-      <c r="K52" s="3">
-        <v>30600</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>32100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>30700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>31800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>36500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>38000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>41900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>46800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>55200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>47200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>56600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>65900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>70700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>77500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>80000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>86800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>93800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>99700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>101900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>105300</v>
       </c>
     </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,94 +4420,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1116800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1078200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1052000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1007300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1026000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1013700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>963000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>957400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>899200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>856100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>843800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>847400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>836400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>786400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>750400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>721500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>683800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>655100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>606500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>599100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>598800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>561800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>530200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>482500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>461400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>458800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>457300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>447100</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4544,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,117 +4577,121 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E57" s="3">
         <v>13300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>15200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>13300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>13300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>12900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>11900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>11500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>11000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>12400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>13100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>9200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>11300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>11700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4619,203 +4753,212 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>121600</v>
+        <v>59700</v>
       </c>
       <c r="E59" s="3">
-        <v>130700</v>
+        <v>61900</v>
       </c>
       <c r="F59" s="3">
-        <v>100300</v>
+        <v>78000</v>
       </c>
       <c r="G59" s="3">
-        <v>124700</v>
+        <v>41200</v>
       </c>
       <c r="H59" s="3">
-        <v>145300</v>
+        <v>51300</v>
       </c>
       <c r="I59" s="3">
-        <v>120000</v>
+        <v>83000</v>
       </c>
       <c r="J59" s="3">
+        <v>64800</v>
+      </c>
+      <c r="K59" s="3">
         <v>149900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>127100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>97800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>98200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>129400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>121800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>106200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>92500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>90600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>85600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>98500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>82700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>92300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>121100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>116100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>79500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>87900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>79000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>94600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>102400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>104200</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>141200</v>
+      </c>
+      <c r="E60" s="3">
         <v>134900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>142500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>111000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>139200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>160700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>135100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>163400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>140400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>110200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>110300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>140200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>134400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>117800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>103200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>103800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>98500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>110400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>92300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>103800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>132100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>128500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>92600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>97100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>91600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>105900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>114100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>112700</v>
       </c>
     </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>17300</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>18400</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>16700</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>21300</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>22900</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>24400</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>25800</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4877,94 +5020,100 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>43900</v>
+        <v>22800</v>
       </c>
       <c r="E62" s="3">
-        <v>43400</v>
+        <v>25400</v>
       </c>
       <c r="F62" s="3">
-        <v>54900</v>
+        <v>26700</v>
       </c>
       <c r="G62" s="3">
+        <v>33500</v>
+      </c>
+      <c r="H62" s="3">
+        <v>34300</v>
+      </c>
+      <c r="I62" s="3">
+        <v>36200</v>
+      </c>
+      <c r="J62" s="3">
+        <v>40900</v>
+      </c>
+      <c r="K62" s="3">
+        <v>68100</v>
+      </c>
+      <c r="L62" s="3">
+        <v>52600</v>
+      </c>
+      <c r="M62" s="3">
+        <v>53100</v>
+      </c>
+      <c r="N62" s="3">
+        <v>55100</v>
+      </c>
+      <c r="O62" s="3">
         <v>57100</v>
       </c>
-      <c r="H62" s="3">
-        <v>60500</v>
-      </c>
-      <c r="I62" s="3">
-        <v>66700</v>
-      </c>
-      <c r="J62" s="3">
-        <v>68100</v>
-      </c>
-      <c r="K62" s="3">
-        <v>52600</v>
-      </c>
-      <c r="L62" s="3">
-        <v>53100</v>
-      </c>
-      <c r="M62" s="3">
-        <v>55100</v>
-      </c>
-      <c r="N62" s="3">
-        <v>57100</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>56600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>55000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>58800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>61800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>63600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>66000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>69100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>64000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>64700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>52100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>57200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>30200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>30100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>30000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>30300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5198,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5287,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,94 +5376,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>181300</v>
+      </c>
+      <c r="E66" s="3">
         <v>178700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>185900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>165900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>196400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>221200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>201800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>231500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>193000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>163300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>165400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>197300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>191000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>172800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>162000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>165600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>162100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>176400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>161400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>167900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>196900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>180600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>149800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>127300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>121700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>135900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>144400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>150900</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5500,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5587,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5676,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5597,8 +5765,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,94 +5854,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>573000</v>
+      </c>
+      <c r="E72" s="3">
         <v>543600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>512600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>480600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>470800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>437000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>382300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>347800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>331900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>309800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>284100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>252000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>227500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>199700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>173100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>142300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>115300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>75300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>47200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>18100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-9400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-27700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-27100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-52900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-67000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-81900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-90600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-108100</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6032,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6121,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,94 +6210,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>935400</v>
+      </c>
+      <c r="E76" s="3">
         <v>899500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>866100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>841400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>829700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>792400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>761200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>725800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>706200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>692800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>678400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>650100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>645400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>613600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>588300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>555900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>521700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>478700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>445100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>431300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>401900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>381200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>380300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>355200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>339600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>322900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>313000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>296200</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6388,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E81" s="3">
         <v>38400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>39400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>17200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>41300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>54700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>34500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>16000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>22100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>25800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>32100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>24500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>27800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>26600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>30800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>27100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>39900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>28200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>29100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>27500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>18200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>24800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>14100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>14900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>8800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>17500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,52 +6606,53 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3100</v>
+        <v>3900</v>
       </c>
       <c r="E83" s="3">
-        <v>3000</v>
+        <v>4400</v>
       </c>
       <c r="F83" s="3">
-        <v>3400</v>
+        <v>5200</v>
       </c>
       <c r="G83" s="3">
-        <v>3900</v>
+        <v>4900</v>
       </c>
       <c r="H83" s="3">
-        <v>4400</v>
+        <v>5100</v>
       </c>
       <c r="I83" s="3">
-        <v>5200</v>
+        <v>4900</v>
       </c>
       <c r="J83" s="3">
         <v>4900</v>
       </c>
       <c r="K83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="L83" s="3">
         <v>5100</v>
-      </c>
-      <c r="L83" s="3">
-        <v>4900</v>
       </c>
       <c r="M83" s="3">
         <v>4900</v>
       </c>
       <c r="N83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="O83" s="3">
         <v>5000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>3900</v>
       </c>
       <c r="P83" s="3">
         <v>3900</v>
       </c>
       <c r="Q83" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="R83" s="3">
         <v>4000</v>
@@ -6462,40 +6661,43 @@
         <v>4000</v>
       </c>
       <c r="T83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="U83" s="3">
         <v>4200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2300</v>
-      </c>
-      <c r="X83" s="3">
-        <v>2200</v>
       </c>
       <c r="Y83" s="3">
         <v>2200</v>
       </c>
       <c r="Z83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AA83" s="3">
         <v>2300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>2100</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>2600</v>
       </c>
       <c r="AD83" s="3">
         <v>2600</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6782,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6871,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6960,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7049,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,94 +7138,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E89" s="3">
         <v>38500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>54500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>32600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>61600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>40500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>52900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>32600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>22200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>46900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>61500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>38000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>44700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>42200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>28400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>60600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>48800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-12300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>32000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>40500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>12900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>38700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>11100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,94 +7262,98 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-1400</v>
       </c>
       <c r="AC91" s="3">
         <v>-1400</v>
       </c>
       <c r="AD91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7438,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,94 +7527,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>67400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-29300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-30800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-57300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-21400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-71000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-46100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-62700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-146900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>30000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>118600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-31700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-62600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>1600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-62000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-7600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-97900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>47000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-7000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-28200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-38400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>5300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,31 +7651,32 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-7400</v>
+        <v>8500</v>
       </c>
       <c r="E96" s="3">
-        <v>-7200</v>
+        <v>7400</v>
       </c>
       <c r="F96" s="3">
-        <v>-7200</v>
+        <v>7200</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+        <v>7200</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7504,8 +7738,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7827,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7916,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,117 +8005,123 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-15900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-11000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-11700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-8800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-23300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-17600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1000</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7932,92 +8181,98 @@
         <v>0</v>
       </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>109900</v>
+      </c>
+      <c r="E102" s="3">
         <v>2100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-55100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>24100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>50700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-19600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-30400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-41700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-133500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>53600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>180300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-19700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>47600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-33400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>53600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-66800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>31300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>26000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>12300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>6400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>9000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>6100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PRDO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRDO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>PRDO</t>
   </si>
@@ -656,404 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>176400</v>
+      </c>
+      <c r="E8" s="3">
         <v>169800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>166700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>168300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>147900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>179900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>186600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>195600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>176100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>168400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>167700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>183000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>159900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>174000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>175500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>183600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>171200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>169100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>176000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>171000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>158500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>155000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>156400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>157900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>145500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>145700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>142000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>148100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>143100</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E9" s="3">
         <v>26600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>26100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>27600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>27700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>31000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>30200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>31100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>31200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>30100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>27300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>28100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>25300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>26000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>28500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>29000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>28600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>27600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>28700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>26900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>24900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>25300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>25400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>26300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>25500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>27200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>30300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>26900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>144500</v>
+      </c>
+      <c r="E10" s="3">
         <v>143200</v>
-      </c>
-      <c r="E10" s="3">
-        <v>140700</v>
       </c>
       <c r="F10" s="3">
         <v>140700</v>
       </c>
       <c r="G10" s="3">
+        <v>140700</v>
+      </c>
+      <c r="H10" s="3">
         <v>120200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>148900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>156300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>164500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>144900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>138300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>140400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>154900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>134600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>148000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>147000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>154600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>142600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>141500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>147300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>144100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>133600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>129700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>131100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>131600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>120000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>118500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>111700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>121200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>114100</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1085,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1174,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,47 +1279,50 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1600</v>
       </c>
-      <c r="G14" s="3">
-        <v>-16600</v>
-      </c>
       <c r="H14" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="I14" s="3">
         <v>7400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-21300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2800</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1316,17 +1335,17 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>600</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
@@ -1337,11 +1356,11 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AA14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
@@ -1349,58 +1368,61 @@
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>3100</v>
+        <v>5500</v>
       </c>
       <c r="E15" s="3">
         <v>3100</v>
       </c>
       <c r="F15" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G15" s="3">
         <v>3000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5100</v>
-      </c>
-      <c r="M15" s="3">
-        <v>4900</v>
       </c>
       <c r="N15" s="3">
         <v>4900</v>
       </c>
       <c r="O15" s="3">
+        <v>4900</v>
+      </c>
+      <c r="P15" s="3">
         <v>5000</v>
-      </c>
-      <c r="P15" s="3">
-        <v>3900</v>
       </c>
       <c r="Q15" s="3">
         <v>3900</v>
       </c>
       <c r="R15" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="S15" s="3">
         <v>4000</v>
@@ -1409,40 +1431,43 @@
         <v>4000</v>
       </c>
       <c r="U15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="V15" s="3">
         <v>4200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2300</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>2200</v>
       </c>
       <c r="Z15" s="3">
         <v>2200</v>
       </c>
       <c r="AA15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AB15" s="3">
         <v>2300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>2400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>2100</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>2600</v>
       </c>
       <c r="AE15" s="3">
         <v>2600</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>137300</v>
+      </c>
+      <c r="E17" s="3">
         <v>125000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>119900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>120400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>126400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>129500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>137700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>151700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>153500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>139100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>133700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>139300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>125300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>136100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>139600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>143000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>135000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>137100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>138700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>133700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>126400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>130700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>156300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>127900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>125300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>126400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>130700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>127500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>132400</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>39200</v>
+      </c>
+      <c r="E18" s="3">
         <v>44800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>46800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>47900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>21500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>50500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>48900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>43900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>22600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>29300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>34000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>43700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>34600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>37900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>35900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>40600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>36200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>32000</v>
-      </c>
-      <c r="U18" s="3">
-        <v>37300</v>
       </c>
       <c r="V18" s="3">
         <v>37300</v>
       </c>
       <c r="W18" s="3">
+        <v>37300</v>
+      </c>
+      <c r="X18" s="3">
         <v>32100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>24300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>30000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>20200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>19300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>11300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>20600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,8 +1714,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1694,174 +1727,180 @@
         <v>100</v>
       </c>
       <c r="F20" s="3">
+        <v>100</v>
+      </c>
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>22000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>1900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>900</v>
-      </c>
-      <c r="N20" s="3">
-        <v>200</v>
       </c>
       <c r="O20" s="3">
         <v>200</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>500</v>
-      </c>
-      <c r="S20" s="3">
-        <v>700</v>
       </c>
       <c r="T20" s="3">
         <v>700</v>
       </c>
       <c r="U20" s="3">
+        <v>700</v>
+      </c>
+      <c r="V20" s="3">
         <v>1200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E21" s="3">
         <v>47800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>49800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>51000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>54300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>53200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>49100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>29400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>36500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>39700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>48800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>39700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>41800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>40200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>45100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>40900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>36800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>42700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>41400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>36000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>28400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>33900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>23700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>22600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>14000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>24100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>14100</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1872,10 +1911,10 @@
         <v>100</v>
       </c>
       <c r="F22" s="3">
+        <v>100</v>
+      </c>
+      <c r="G22" s="3">
         <v>300</v>
-      </c>
-      <c r="G22" s="3">
-        <v>100</v>
       </c>
       <c r="H22" s="3">
         <v>100</v>
@@ -1898,21 +1937,21 @@
       <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3" t="s">
+      <c r="O22" s="3">
+        <v>100</v>
+      </c>
+      <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
       <c r="T22" s="3">
         <v>0</v>
       </c>
@@ -1935,10 +1974,10 @@
         <v>0</v>
       </c>
       <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3">
         <v>400</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>100</v>
       </c>
       <c r="AC22" s="3">
         <v>100</v>
@@ -1949,186 +1988,195 @@
       <c r="AE22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>43200</v>
+      </c>
+      <c r="E23" s="3">
         <v>52400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>53000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>52900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>22400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>48100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>74600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>47100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>24400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>31300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>34700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>43800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>34800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>37300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>36000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>41000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>36900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>32800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>38500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>38700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>33600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>26000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>31600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>21000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>20200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>11800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>21400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E24" s="3">
         <v>14100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>13400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>19900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>12600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>8500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>11800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>10300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>9600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>10200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>9800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-7200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>10300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>9600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>6100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>6400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>7000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E26" s="3">
         <v>38300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>38400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>39400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>17200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>41300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>54700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>34500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>16000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>22100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>25800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>32100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>24500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>27800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>26700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>30800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>27100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>40000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>28200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>29100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>27500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>18400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>25200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>14000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>15100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>8900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>17900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E27" s="3">
         <v>38300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>38400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>39400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>17200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>41300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>54700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>34500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>16000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>22100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>25800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>32100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>24500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>27800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>26700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>30800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>27100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>40000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>28200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>29100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>27500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>18400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>25200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>14000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>15100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>8900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>17900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2509,8 +2569,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -2521,8 +2581,8 @@
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -2549,31 +2609,34 @@
         <v>0</v>
       </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-200</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-400</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>100</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-200</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-100</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-400</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-52400</v>
       </c>
     </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,8 +2816,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2762,174 +2831,180 @@
         <v>-100</v>
       </c>
       <c r="F32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-22000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-900</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-200</v>
       </c>
       <c r="O32" s="3">
         <v>-200</v>
       </c>
       <c r="P32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-500</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-700</v>
       </c>
       <c r="T32" s="3">
         <v>-700</v>
       </c>
       <c r="U32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="V32" s="3">
         <v>-1200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E33" s="3">
         <v>38300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>38400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>39400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>17200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>41300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>54700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>34500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>16000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>22100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>25800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>32100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>24500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>27800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>26600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>30800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>27100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>39900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>28200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>29100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>27500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>18200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>24800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>14100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>14900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>8800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>17500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E35" s="3">
         <v>38300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>38400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>39400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>17200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>41300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>54700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>34500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>16000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>22100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>25800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>32100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>24500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>27800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>26600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>30800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>27100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>39900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>28200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>29100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>27500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>18200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>24800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>14100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>14900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>8800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>17500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,319 +3351,329 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>109100</v>
+      </c>
+      <c r="E41" s="3">
         <v>238000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>127900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>125800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>118000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>165600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>140500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>89800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>109400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>147100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>148700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>190400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>320000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>266400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>87300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>86000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>105700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>58100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>91500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>37900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>108700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>47400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>51100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>38800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>32400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>32000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>33200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>24200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>459800</v>
+      </c>
+      <c r="E42" s="3">
         <v>483800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>546300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>515600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>485100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>429600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>428100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>420900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>399300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>375900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>366800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>307600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>174200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>209400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>389300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>361000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>300700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>305600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>250300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>243700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>185500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>234400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>228800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>200800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>196400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>156300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>151600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>158000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>156200</v>
       </c>
     </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E43" s="3">
         <v>36100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>39800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>47200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>33900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>53300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>49200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>49300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>46000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>45300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>40800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>42900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>44700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>44400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>54300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>44200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>47600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>40300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>37100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>34100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>56400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>31200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>30500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>32400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>31300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>36500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>26900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>25300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E44" s="3">
         <v>3900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>600</v>
       </c>
       <c r="R44" s="3">
         <v>600</v>
@@ -3599,7 +3694,7 @@
         <v>600</v>
       </c>
       <c r="X44" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="Y44" s="3">
         <v>700</v>
@@ -3608,229 +3703,238 @@
         <v>700</v>
       </c>
       <c r="AA44" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB44" s="3">
         <v>800</v>
-      </c>
-      <c r="AB44" s="3">
-        <v>900</v>
       </c>
       <c r="AC44" s="3">
         <v>900</v>
       </c>
       <c r="AD44" s="3">
+        <v>900</v>
+      </c>
+      <c r="AE44" s="3">
         <v>1000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>200</v>
+      </c>
+      <c r="E45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>500</v>
-      </c>
-      <c r="F45" s="3">
-        <v>200</v>
       </c>
       <c r="G45" s="3">
         <v>200</v>
       </c>
       <c r="H45" s="3">
+        <v>200</v>
+      </c>
+      <c r="I45" s="3">
         <v>300</v>
-      </c>
-      <c r="I45" s="3">
-        <v>700</v>
       </c>
       <c r="J45" s="3">
         <v>700</v>
       </c>
       <c r="K45" s="3">
+        <v>700</v>
+      </c>
+      <c r="L45" s="3">
         <v>18500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>12000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>15800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>14300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>12600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>12200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>14600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>16000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>9200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>39300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>9800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>9500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>8500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>14400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>18100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>16900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>15300</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>640200</v>
+      </c>
+      <c r="E46" s="3">
         <v>773500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>732500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>706000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>655000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>669600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>643400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>585400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>575100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>582300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>571800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>556200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>554500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>537100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>549100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>506100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>467100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>416900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>394100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>332300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>360400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>353000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>320900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>282200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>269400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>240100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>230700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>225400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>210700</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>1200</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E47" s="3">
         <v>1200</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="F47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>1000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>1200</v>
       </c>
       <c r="J47" s="3">
         <v>1200</v>
       </c>
       <c r="K47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L47" s="3">
         <v>1900</v>
-      </c>
-      <c r="L47" s="3">
-        <v>1300</v>
       </c>
       <c r="M47" s="3">
         <v>1300</v>
@@ -3839,209 +3943,215 @@
         <v>1300</v>
       </c>
       <c r="O47" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="P47" s="3">
         <v>1400</v>
       </c>
       <c r="Q47" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R47" s="3">
         <v>1500</v>
-      </c>
-      <c r="R47" s="3">
-        <v>1300</v>
       </c>
       <c r="S47" s="3">
         <v>1300</v>
       </c>
       <c r="T47" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="U47" s="3">
         <v>1200</v>
       </c>
       <c r="V47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="W47" s="3">
         <v>1100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>161000</v>
+      </c>
+      <c r="E48" s="3">
         <v>33800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>35500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>34900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>40500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>45600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>47400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>50000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>52200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>56600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>59400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>62500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>65000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>64600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>65600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>68100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>72500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>75900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>77200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>79400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>76400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>78700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>67600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>71800</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>30000</v>
       </c>
       <c r="AB48" s="3">
         <v>30000</v>
       </c>
       <c r="AC48" s="3">
+        <v>30000</v>
+      </c>
+      <c r="AD48" s="3">
         <v>30800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>32000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>33200</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>353000</v>
+      </c>
+      <c r="E49" s="3">
         <v>274100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>275200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>276300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>277400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>281100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>293200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>294900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>297100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>228400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>191500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>193100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>194800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>196800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>132200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>133000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>133800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>134700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>135500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>137100</v>
-      </c>
-      <c r="W49" s="3">
-        <v>95300</v>
       </c>
       <c r="X49" s="3">
         <v>95300</v>
@@ -4067,8 +4177,11 @@
       <c r="AE49" s="3">
         <v>95300</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>95300</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,97 +4361,103 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5300</v>
+        <v>7900</v>
       </c>
       <c r="E52" s="3">
         <v>5300</v>
       </c>
       <c r="F52" s="3">
+        <v>5300</v>
+      </c>
+      <c r="G52" s="3">
         <v>6800</v>
       </c>
-      <c r="G52" s="3">
-        <v>5600</v>
-      </c>
       <c r="H52" s="3">
+        <v>6800</v>
+      </c>
+      <c r="I52" s="3">
         <v>4200</v>
-      </c>
-      <c r="I52" s="3">
-        <v>5700</v>
       </c>
       <c r="J52" s="3">
         <v>5700</v>
       </c>
       <c r="K52" s="3">
+        <v>5700</v>
+      </c>
+      <c r="L52" s="3">
         <v>31100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>30600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>32100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>30700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>31800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>36500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>38000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>41900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>46800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>55200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>47200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>56600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>65900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>70700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>77500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>80000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>86800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>93800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>99700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>101900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>105300</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1237000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1116800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1078200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1052000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1007300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1026000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1013700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>963000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>957400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>899200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>856100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>843800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>847400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>836400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>786400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>750400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>721500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>683800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>655100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>606500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>599100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>598800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>561800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>530200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>482500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>461400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>458800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>457300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>447100</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,124 +4707,128 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E57" s="3">
         <v>13600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>15400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>15200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>13500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>11500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>13300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>12900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>11500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>11000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>12400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>13100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>9200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>11300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>11700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E58" s="3">
         <v>5000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -4756,213 +4889,222 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E59" s="3">
         <v>59700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>61900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>78000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>41200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>51300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>83000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>64800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>149900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>127100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>97800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>98200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>129400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>121800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>106200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>92500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>90600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>85600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>98500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>82700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>92300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>121100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>116100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>79500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>87900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>79000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>94600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>102400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>104200</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>132200</v>
+      </c>
+      <c r="E60" s="3">
         <v>141200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>134900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>142500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>111000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>139200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>160700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>135100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>163400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>140400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>110200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>110300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>140200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>134400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>117800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>103200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>103800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>98500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>110400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>92300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>103800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>132100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>128500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>92600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>97100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>91600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>105900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>114100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>112700</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>118300</v>
+      </c>
+      <c r="E61" s="3">
         <v>17300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>21300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>22900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>24400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>25800</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5023,97 +5165,103 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E62" s="3">
         <v>22800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>25400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>26700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>33500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>34300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>36200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>40900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>68100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>52600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>53100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>55100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>57100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>56600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>55000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>58800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>61800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>63600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>66000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>69100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>64000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>64700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>52100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>57200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>30200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>30100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>30000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>30300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,97 +5533,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>277500</v>
+      </c>
+      <c r="E66" s="3">
         <v>181300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>178700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>185900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>165900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>196400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>221200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>201800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>231500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>193000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>163300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>165400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>197300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>191000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>172800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>162000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>165600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>162100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>176400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>161400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>167900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>196900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>180600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>149800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>127300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>121700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>135900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>144400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>150900</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5768,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,97 +6027,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>595700</v>
+      </c>
+      <c r="E72" s="3">
         <v>573000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>543600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>512600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>480600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>470800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>437000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>382300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>347800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>331900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>309800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>284100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>252000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>227500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>199700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>173100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>142300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>115300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>75300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>47200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>18100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-27700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-27100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-52900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-67000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-81900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-90600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-108100</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>959500</v>
+      </c>
+      <c r="E76" s="3">
         <v>935400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>899500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>866100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>841400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>829700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>792400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>761200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>725800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>706200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>692800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>678400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>650100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>645400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>613600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>588300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>555900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>521700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>478700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>445100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>431300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>401900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>381200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>380300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>355200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>339600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>322900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>313000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>296200</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E81" s="3">
         <v>38300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>38400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>39400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>17200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>41300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>54700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>34500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>16000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>22100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>25800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>32100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>24500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>27800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>26600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>30800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>27100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>39900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>28200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>29100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>27500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>18200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>24800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>14100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>14900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>8800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>17500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,28 +6804,29 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E83" s="3">
         <v>3900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>4900</v>
       </c>
       <c r="J83" s="3">
         <v>4900</v>
@@ -6637,25 +6835,25 @@
         <v>4900</v>
       </c>
       <c r="L83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="M83" s="3">
         <v>5100</v>
-      </c>
-      <c r="M83" s="3">
-        <v>4900</v>
       </c>
       <c r="N83" s="3">
         <v>4900</v>
       </c>
       <c r="O83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="P83" s="3">
         <v>5000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>3900</v>
       </c>
       <c r="Q83" s="3">
         <v>3900</v>
       </c>
       <c r="R83" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="S83" s="3">
         <v>4000</v>
@@ -6664,40 +6862,43 @@
         <v>4000</v>
       </c>
       <c r="U83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="V83" s="3">
         <v>4200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2300</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>2200</v>
       </c>
       <c r="Z83" s="3">
         <v>2200</v>
       </c>
       <c r="AA83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AB83" s="3">
         <v>2300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>2400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2100</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>2600</v>
       </c>
       <c r="AE83" s="3">
         <v>2600</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E89" s="3">
         <v>51000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>38500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>54500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>32600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>61600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>40500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>52900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>32600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>22200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>46900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>61500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>38000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>44700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>42200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>28400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>60600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>48800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-12300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>32000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>40500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>12900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>38700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>11100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,97 +7482,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>-1400</v>
       </c>
       <c r="AD91" s="3">
         <v>-1400</v>
       </c>
       <c r="AE91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,97 +7756,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-115100</v>
+      </c>
+      <c r="E94" s="3">
         <v>67400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-29300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-30800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-57300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-21400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-71000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-46100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-62700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-146900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>30000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>118600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-31700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-62600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>1600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-62000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-7600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-97900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>47000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-28200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-38400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>5300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7661,10 +7894,10 @@
         <v>8500</v>
       </c>
       <c r="E96" s="3">
+        <v>8500</v>
+      </c>
+      <c r="F96" s="3">
         <v>7400</v>
-      </c>
-      <c r="F96" s="3">
-        <v>7200</v>
       </c>
       <c r="G96" s="3">
         <v>7200</v>
@@ -7672,14 +7905,14 @@
       <c r="H96" s="3">
         <v>7200</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>8</v>
+      <c r="I96" s="3">
+        <v>7200</v>
       </c>
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7741,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,97 +8250,103 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-15900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-11000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-11700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-8800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-23300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>3800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-17600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-3500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1000</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8123,8 +8371,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -8184,95 +8432,101 @@
         <v>0</v>
       </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-107100</v>
+      </c>
+      <c r="E102" s="3">
         <v>109900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-55100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>24100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>50700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-19600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-30400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-41700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-133500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>53600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>180300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-19700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>47600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-33400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>53600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-66800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>31300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>26000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>12300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>6400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>9000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>6100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PRDO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRDO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>PRDO</t>
   </si>
@@ -656,416 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>213000</v>
+      </c>
+      <c r="E8" s="3">
         <v>176400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>169800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>166700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>168300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>147900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>179900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>186600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>195600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>176100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>168400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>167700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>183000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>159900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>174000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>175500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>183600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>171200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>169100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>176000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>171000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>158500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>155000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>156400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>157900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>145500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>145700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>142000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>148100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>143100</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>42100</v>
+      </c>
+      <c r="E9" s="3">
         <v>31900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>26600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>26100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>27600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>27700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>31000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>30200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>31100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>31200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>30100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>27300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>28100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>25300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>26000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>28500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>29000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>28600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>27600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>28700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>26900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>24900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>25300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>25400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>26300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>25500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>27200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>30300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>26900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>170900</v>
+      </c>
+      <c r="E10" s="3">
         <v>144500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>143200</v>
-      </c>
-      <c r="F10" s="3">
-        <v>140700</v>
       </c>
       <c r="G10" s="3">
         <v>140700</v>
       </c>
       <c r="H10" s="3">
+        <v>140700</v>
+      </c>
+      <c r="I10" s="3">
         <v>120200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>148900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>156300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>164500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>144900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>138300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>140400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>154900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>134600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>148000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>147000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>154600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>142600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>141500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>147300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>144100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>133600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>129700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>131100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>131600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>120000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>118500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>111700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>121200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>114100</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,50 +1299,53 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>3100</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-16500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>7400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-21300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2800</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>200</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1338,17 +1358,17 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>600</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
@@ -1359,11 +1379,11 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3" t="s">
+      <c r="AB14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
@@ -1371,61 +1391,64 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E15" s="3">
         <v>5500</v>
-      </c>
-      <c r="E15" s="3">
-        <v>3100</v>
       </c>
       <c r="F15" s="3">
         <v>3100</v>
       </c>
       <c r="G15" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H15" s="3">
         <v>3000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5100</v>
-      </c>
-      <c r="N15" s="3">
-        <v>4900</v>
       </c>
       <c r="O15" s="3">
         <v>4900</v>
       </c>
       <c r="P15" s="3">
+        <v>4900</v>
+      </c>
+      <c r="Q15" s="3">
         <v>5000</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>3900</v>
       </c>
       <c r="R15" s="3">
         <v>3900</v>
       </c>
       <c r="S15" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="T15" s="3">
         <v>4000</v>
@@ -1434,40 +1457,43 @@
         <v>4000</v>
       </c>
       <c r="V15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="W15" s="3">
         <v>4200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2300</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>2200</v>
       </c>
       <c r="AA15" s="3">
         <v>2200</v>
       </c>
       <c r="AB15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AC15" s="3">
         <v>2300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>2400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>2100</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>2600</v>
       </c>
       <c r="AF15" s="3">
         <v>2600</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>161300</v>
+      </c>
+      <c r="E17" s="3">
         <v>137300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>125000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>119900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>120400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>126400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>129500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>137700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>151700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>153500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>139100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>133700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>139300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>125300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>136100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>139600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>143000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>135000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>137100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>138700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>133700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>126400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>130700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>156300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>127900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>125300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>126400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>130700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>127500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>132400</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E18" s="3">
         <v>39200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>44800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>46800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>47900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>21500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>50500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>48900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>43900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>22600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>29300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>34000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>43700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>34600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>37900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>35900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>40600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>36200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>32000</v>
-      </c>
-      <c r="V18" s="3">
-        <v>37300</v>
       </c>
       <c r="W18" s="3">
         <v>37300</v>
       </c>
       <c r="X18" s="3">
+        <v>37300</v>
+      </c>
+      <c r="Y18" s="3">
         <v>32100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>24300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>30000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>20200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>19300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>11300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>20600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,13 +1748,14 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
         <v>100</v>
@@ -1730,182 +1764,188 @@
         <v>100</v>
       </c>
       <c r="G20" s="3">
+        <v>100</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>22000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>1900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>900</v>
-      </c>
-      <c r="O20" s="3">
-        <v>200</v>
       </c>
       <c r="P20" s="3">
         <v>200</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>500</v>
-      </c>
-      <c r="T20" s="3">
-        <v>700</v>
       </c>
       <c r="U20" s="3">
         <v>700</v>
       </c>
       <c r="V20" s="3">
+        <v>700</v>
+      </c>
+      <c r="W20" s="3">
         <v>1200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>63500</v>
+      </c>
+      <c r="E21" s="3">
         <v>44600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>47800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>49800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>51000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>54300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>53200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>49100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>29400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>36500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>39700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>48800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>39700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>41800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>40200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>45100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>40900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>36800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>42700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>41400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>36000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>28400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>33900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>23700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>22600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>14000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>24100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>14100</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>100</v>
+        <v>1700</v>
       </c>
       <c r="E22" s="3">
         <v>100</v>
@@ -1914,10 +1954,10 @@
         <v>100</v>
       </c>
       <c r="G22" s="3">
+        <v>100</v>
+      </c>
+      <c r="H22" s="3">
         <v>300</v>
-      </c>
-      <c r="H22" s="3">
-        <v>100</v>
       </c>
       <c r="I22" s="3">
         <v>100</v>
@@ -1940,21 +1980,21 @@
       <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3" t="s">
+      <c r="P22" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
       <c r="U22" s="3">
         <v>0</v>
       </c>
@@ -1977,10 +2017,10 @@
         <v>0</v>
       </c>
       <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
         <v>400</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>100</v>
       </c>
       <c r="AD22" s="3">
         <v>100</v>
@@ -1991,192 +2031,201 @@
       <c r="AF22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>56500</v>
+      </c>
+      <c r="E23" s="3">
         <v>43200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>52400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>53000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>52900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>22400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>48100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>74600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>47100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>24400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>31300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>34700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>43800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>34800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>37300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>36000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>41000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>36900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>32800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>38500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>38700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>33600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>26000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>31600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>21000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>20200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>11800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>21400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E24" s="3">
         <v>11700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>14600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>13400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>19900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>12600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>8500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>11800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>10300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>9300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>10200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>9800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-7200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>10300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>9600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>6400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>7000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>5100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E26" s="3">
         <v>31500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>38300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>38400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>39400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>17200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>41300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>54700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>34500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>16000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>22100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>25800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>32100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>24500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>27800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>26700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>30800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>27100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>40000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>28200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>29100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>27500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>18400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>25200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>14000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>15100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>8900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>17900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E27" s="3">
         <v>31500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>38300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>38400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>39400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>17200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>41300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>54700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>34500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>16000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>22100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>25800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>32100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>24500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>27800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>26700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>30800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>27100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>40000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>28200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>29100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>27500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>18400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>25200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>14000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>15100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>8900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>17900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2572,8 +2633,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -2584,8 +2645,8 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -2612,31 +2673,34 @@
         <v>0</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-200</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-400</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>100</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-200</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-100</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-400</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-52400</v>
       </c>
     </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,13 +2886,16 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <v>-100</v>
@@ -2834,177 +2904,183 @@
         <v>-100</v>
       </c>
       <c r="G32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-22000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-1900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-900</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-200</v>
       </c>
       <c r="P32" s="3">
         <v>-200</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-500</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-700</v>
       </c>
       <c r="U32" s="3">
         <v>-700</v>
       </c>
       <c r="V32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="W32" s="3">
         <v>-1200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E33" s="3">
         <v>31500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>38300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>38400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>39400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>17200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>41300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>54700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>34500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>16000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>22100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>25800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>32100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>24500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>27800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>26600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>30800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>27100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>39900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>28200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>29100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>27500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>18200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>24800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>14100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>14900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>8800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>17500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E35" s="3">
         <v>31500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>38300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>38400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>39400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>17200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>41300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>54700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>34500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>16000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>22100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>25800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>32100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>24500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>27800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>26600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>30800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>27100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>39900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>28200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>29100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>27500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>18200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>24800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>14100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>14900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>8800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>17500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,331 +3438,341 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>132100</v>
+      </c>
+      <c r="E41" s="3">
         <v>109100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>238000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>127900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>125800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>118000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>165600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>140500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>89800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>109400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>147100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>148700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>190400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>320000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>266400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>87300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>86000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>105700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>58100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>91500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>37900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>108700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>47400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>51100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>38800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>32400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>32000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>33200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>24200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>458500</v>
+      </c>
+      <c r="E42" s="3">
         <v>459800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>483800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>546300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>515600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>485100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>429600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>428100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>420900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>399300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>375900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>366800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>307600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>174200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>209400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>389300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>361000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>300700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>305600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>250300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>243700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>185500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>234400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>228800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>200800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>196400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>156300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>151600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>158000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>156200</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>55700</v>
+      </c>
+      <c r="E43" s="3">
         <v>28100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>36100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>39800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>47200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>33900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>53300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>49200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>49300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>46000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>45300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>40800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>42900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>44700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>44400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>54300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>44200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>47600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>40300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>37100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>34100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>56400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>31200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>30500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>32400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>31300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>36500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>26900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>25300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E44" s="3">
         <v>3400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1200</v>
-      </c>
-      <c r="R44" s="3">
-        <v>600</v>
       </c>
       <c r="S44" s="3">
         <v>600</v>
@@ -3697,7 +3793,7 @@
         <v>600</v>
       </c>
       <c r="Y44" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="Z44" s="3">
         <v>700</v>
@@ -3706,22 +3802,25 @@
         <v>700</v>
       </c>
       <c r="AB44" s="3">
+        <v>700</v>
+      </c>
+      <c r="AC44" s="3">
         <v>800</v>
-      </c>
-      <c r="AC44" s="3">
-        <v>900</v>
       </c>
       <c r="AD44" s="3">
         <v>900</v>
       </c>
       <c r="AE44" s="3">
+        <v>900</v>
+      </c>
+      <c r="AF44" s="3">
         <v>1000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3729,215 +3828,221 @@
         <v>200</v>
       </c>
       <c r="E45" s="3">
+        <v>200</v>
+      </c>
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>200</v>
       </c>
       <c r="H45" s="3">
         <v>200</v>
       </c>
       <c r="I45" s="3">
+        <v>200</v>
+      </c>
+      <c r="J45" s="3">
         <v>300</v>
-      </c>
-      <c r="J45" s="3">
-        <v>700</v>
       </c>
       <c r="K45" s="3">
         <v>700</v>
       </c>
       <c r="L45" s="3">
+        <v>700</v>
+      </c>
+      <c r="M45" s="3">
         <v>18500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>12000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>14600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>15800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>17600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>14300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>12600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>12200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>14600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>16000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>9200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>39300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>9800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>9500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>8500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>14400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>18100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>16900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>15300</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>686000</v>
+      </c>
+      <c r="E46" s="3">
         <v>640200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>773500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>732500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>706000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>655000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>669600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>643400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>585400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>575100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>582300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>571800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>556200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>554500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>537100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>549100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>506100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>467100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>416900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>394100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>332300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>360400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>353000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>320900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>282200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>269400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>240100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>230700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>225400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>210700</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3">
-        <v>1200</v>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F47" s="3">
         <v>1200</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>8</v>
+      <c r="G47" s="3">
+        <v>1200</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
         <v>1000</v>
-      </c>
-      <c r="J47" s="3">
-        <v>1200</v>
       </c>
       <c r="K47" s="3">
         <v>1200</v>
       </c>
       <c r="L47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M47" s="3">
         <v>1900</v>
-      </c>
-      <c r="M47" s="3">
-        <v>1300</v>
       </c>
       <c r="N47" s="3">
         <v>1300</v>
@@ -3946,215 +4051,221 @@
         <v>1300</v>
       </c>
       <c r="P47" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="Q47" s="3">
         <v>1400</v>
       </c>
       <c r="R47" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S47" s="3">
         <v>1500</v>
-      </c>
-      <c r="S47" s="3">
-        <v>1300</v>
       </c>
       <c r="T47" s="3">
         <v>1300</v>
       </c>
       <c r="U47" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="V47" s="3">
         <v>1200</v>
       </c>
       <c r="W47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X47" s="3">
         <v>1100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>152000</v>
+      </c>
+      <c r="E48" s="3">
         <v>161000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>33800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>35500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>34900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>40500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>45600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>47400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>50000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>52200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>56600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>59400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>62500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>65000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>64600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>65600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>68100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>72500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>75900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>77200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>79400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>76400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>78700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>67600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>71800</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>30000</v>
       </c>
       <c r="AC48" s="3">
         <v>30000</v>
       </c>
       <c r="AD48" s="3">
+        <v>30000</v>
+      </c>
+      <c r="AE48" s="3">
         <v>30800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>32000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>33200</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>348700</v>
+      </c>
+      <c r="E49" s="3">
         <v>353000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>274100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>275200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>276300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>277400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>281100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>293200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>294900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>297100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>228400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>191500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>193100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>194800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>196800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>132200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>133000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>133800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>134700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>135500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>137100</v>
-      </c>
-      <c r="X49" s="3">
-        <v>95300</v>
       </c>
       <c r="Y49" s="3">
         <v>95300</v>
@@ -4180,8 +4291,11 @@
       <c r="AF49" s="3">
         <v>95300</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>95300</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4481,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4373,91 +4493,94 @@
         <v>7900</v>
       </c>
       <c r="E52" s="3">
-        <v>5300</v>
+        <v>7900</v>
       </c>
       <c r="F52" s="3">
         <v>5300</v>
       </c>
       <c r="G52" s="3">
-        <v>6800</v>
+        <v>5300</v>
       </c>
       <c r="H52" s="3">
         <v>6800</v>
       </c>
       <c r="I52" s="3">
+        <v>6800</v>
+      </c>
+      <c r="J52" s="3">
         <v>4200</v>
-      </c>
-      <c r="J52" s="3">
-        <v>5700</v>
       </c>
       <c r="K52" s="3">
         <v>5700</v>
       </c>
       <c r="L52" s="3">
+        <v>5700</v>
+      </c>
+      <c r="M52" s="3">
         <v>31100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>30600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>32100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>30700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>31800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>36500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>38000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>41900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>46800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>55200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>47200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>56600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>65900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>70700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>77500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>80000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>86800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>93800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>99700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>101900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>105300</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4671,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1268500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1237000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1116800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1078200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1052000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1007300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1026000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1013700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>963000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>957400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>899200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>856100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>843800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>847400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>836400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>786400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>750400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>721500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>683800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>655100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>606500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>599100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>598800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>561800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>530200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>482500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>461400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>458800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>457300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>447100</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,130 +4838,134 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E57" s="3">
         <v>12800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>15400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>15200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>11500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>13300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>12900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>11900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>11500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>11000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>12400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>13100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>9200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>11300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>11700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E58" s="3">
         <v>13300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4892,222 +5026,231 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>80700</v>
+      </c>
+      <c r="E59" s="3">
         <v>41700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>59700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>61900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>78000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>41200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>51300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>83000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>64800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>149900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>127100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>97800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>98200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>129400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>121800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>106200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>92500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>90600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>85600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>98500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>82700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>92300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>121100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>116100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>79500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>87900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>79000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>94600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>102400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>104200</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>154000</v>
+      </c>
+      <c r="E60" s="3">
         <v>132200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>141200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>134900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>142500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>111000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>139200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>160700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>135100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>163400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>140400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>110200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>110300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>140200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>134400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>117800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>103200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>103800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>98500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>110400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>92300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>103800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>132100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>128500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>92600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>97100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>91600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>105900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>114100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>112700</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>117300</v>
+      </c>
+      <c r="E61" s="3">
         <v>118300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>17300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>16700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>21300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>22900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>24400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>25800</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5168,8 +5311,11 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5177,91 +5323,94 @@
         <v>27100</v>
       </c>
       <c r="E62" s="3">
+        <v>27100</v>
+      </c>
+      <c r="F62" s="3">
         <v>22800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>25400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>26700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>33500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>34300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>36200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>40900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>68100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>52600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>53100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>55100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>57100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>56600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>55000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>58800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>61800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>63600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>66000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>69100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>64000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>64700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>52100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>57200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>30200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>30100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>30000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>30300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5691,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>298300</v>
+      </c>
+      <c r="E66" s="3">
         <v>277500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>181300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>178700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>185900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>165900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>196400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>221200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>201800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>231500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>193000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>163300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>165400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>197300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>191000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>172800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>162000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>165600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>162100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>176400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>161400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>167900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>196900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>180600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>149800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>127300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>121700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>135900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>144400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>150900</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6201,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>630500</v>
+      </c>
+      <c r="E72" s="3">
         <v>595700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>573000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>543600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>512600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>480600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>470800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>437000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>382300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>347800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>331900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>309800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>284100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>252000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>227500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>199700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>173100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>142300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>115300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>75300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>47200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>18100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-9400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-27700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-27100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-52900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-67000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-81900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-90600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-108100</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6581,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>970300</v>
+      </c>
+      <c r="E76" s="3">
         <v>959500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>935400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>899500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>866100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>841400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>829700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>792400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>761200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>725800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>706200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>692800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>678400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>650100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>645400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>613600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>588300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>555900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>521700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>478700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>445100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>431300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>401900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>381200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>380300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>355200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>339600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>322900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>313000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>296200</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E81" s="3">
         <v>31500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>38300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>38400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>39400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>17200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>41300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>54700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>34500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>16000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>22100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>25800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>32100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>24500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>27800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>26600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>30800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>27100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>39900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>28200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>29100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>27500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>18200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>24800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>14100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>14900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>8800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>17500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,31 +7003,32 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E83" s="3">
         <v>3400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>4900</v>
       </c>
       <c r="K83" s="3">
         <v>4900</v>
@@ -6838,25 +7037,25 @@
         <v>4900</v>
       </c>
       <c r="M83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="N83" s="3">
         <v>5100</v>
-      </c>
-      <c r="N83" s="3">
-        <v>4900</v>
       </c>
       <c r="O83" s="3">
         <v>4900</v>
       </c>
       <c r="P83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="Q83" s="3">
         <v>5000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>3900</v>
       </c>
       <c r="R83" s="3">
         <v>3900</v>
       </c>
       <c r="S83" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="T83" s="3">
         <v>4000</v>
@@ -6865,40 +7064,43 @@
         <v>4000</v>
       </c>
       <c r="V83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="W83" s="3">
         <v>4200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2300</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>2200</v>
       </c>
       <c r="AA83" s="3">
         <v>2200</v>
       </c>
       <c r="AB83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AC83" s="3">
         <v>2300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>2100</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>2600</v>
       </c>
       <c r="AF83" s="3">
         <v>2600</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E89" s="3">
         <v>17600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>51000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>38500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>54500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>13200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>32600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>61600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>40500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>52900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>32600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>22200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>46900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>61500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>38000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>44700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>42200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>28400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>60600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>48800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-12300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>32000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>40500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>12900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>38700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>11100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7703,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-1400</v>
       </c>
       <c r="AE91" s="3">
         <v>-1400</v>
       </c>
       <c r="AF91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7986,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-115100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>67400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-29300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-30800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-57300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-21400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-71000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-46100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-62700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-146900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>30000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>118600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-31700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-62600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>1600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-62000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-7600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-97900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>47000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-28200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-38400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>5300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,22 +8118,23 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>8500</v>
+        <v>9200</v>
       </c>
       <c r="E96" s="3">
         <v>8500</v>
       </c>
       <c r="F96" s="3">
+        <v>8500</v>
+      </c>
+      <c r="G96" s="3">
         <v>7400</v>
-      </c>
-      <c r="G96" s="3">
-        <v>7200</v>
       </c>
       <c r="H96" s="3">
         <v>7200</v>
@@ -7908,14 +8142,14 @@
       <c r="I96" s="3">
         <v>7200</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
+      <c r="J96" s="3">
+        <v>7200</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,100 +8496,106 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-44400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-8500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-15900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-11000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-11700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-8800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-23300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-5100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>3800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-17600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1000</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8374,8 +8623,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -8435,98 +8684,104 @@
         <v>0</v>
       </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-107100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>109900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>7800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-55100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>24100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>50700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-19600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-30400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-41700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-133500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>53600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>180300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-19700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>47600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-33400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>53600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-66800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>31300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>26000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>12300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>6400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>9000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>6100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PRDO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRDO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>PRDO</t>
   </si>
@@ -656,429 +656,442 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>209600</v>
+      </c>
+      <c r="E8" s="3">
         <v>213000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>176400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>169800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>166700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>168300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>147900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>179900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>186600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>195600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>176100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>168400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>167700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>183000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>159900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>174000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>175500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>183600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>171200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>169100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>176000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>171000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>158500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>155000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>156400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>157900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>145500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>145700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>142000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>148100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>143100</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>44300</v>
+      </c>
+      <c r="E9" s="3">
         <v>42100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>31900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>26600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>26100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>27600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>27700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>31000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>30200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>31100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>31200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>30100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>27300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>28100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>25300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>26000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>28500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>29000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>28600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>27600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>28700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>26900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>24900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>25300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>25400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>26300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>25500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>27200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>30300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>26900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>165200</v>
+      </c>
+      <c r="E10" s="3">
         <v>170900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>144500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>143200</v>
-      </c>
-      <c r="G10" s="3">
-        <v>140700</v>
       </c>
       <c r="H10" s="3">
         <v>140700</v>
       </c>
       <c r="I10" s="3">
+        <v>140700</v>
+      </c>
+      <c r="J10" s="3">
         <v>120200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>148900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>156300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>164500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>144900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>138300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>140400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>154900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>134600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>148000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>147000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>154600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>142600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>141500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>147300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>144100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>133600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>129700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>131100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>131600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>120000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>118500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>111700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>121200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>114100</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,8 +1125,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1221,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,53 +1319,56 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>3100</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-16500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>7400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-21300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2800</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1361,17 +1381,17 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>600</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
@@ -1382,11 +1402,11 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
+      <c r="AC14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
@@ -1394,64 +1414,67 @@
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E15" s="3">
         <v>11800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5500</v>
-      </c>
-      <c r="F15" s="3">
-        <v>3100</v>
       </c>
       <c r="G15" s="3">
         <v>3100</v>
       </c>
       <c r="H15" s="3">
+        <v>3100</v>
+      </c>
+      <c r="I15" s="3">
         <v>3000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5100</v>
-      </c>
-      <c r="O15" s="3">
-        <v>4900</v>
       </c>
       <c r="P15" s="3">
         <v>4900</v>
       </c>
       <c r="Q15" s="3">
+        <v>4900</v>
+      </c>
+      <c r="R15" s="3">
         <v>5000</v>
-      </c>
-      <c r="R15" s="3">
-        <v>3900</v>
       </c>
       <c r="S15" s="3">
         <v>3900</v>
       </c>
       <c r="T15" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="U15" s="3">
         <v>4000</v>
@@ -1460,40 +1483,43 @@
         <v>4000</v>
       </c>
       <c r="W15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="X15" s="3">
         <v>4200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2300</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>2200</v>
       </c>
       <c r="AB15" s="3">
         <v>2200</v>
       </c>
       <c r="AC15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AD15" s="3">
         <v>2300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>2400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>2100</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>2600</v>
       </c>
       <c r="AG15" s="3">
         <v>2600</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1550,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>158200</v>
+      </c>
+      <c r="E17" s="3">
         <v>161300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>137300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>125000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>119900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>120400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>126400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>129500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>137700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>151700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>153500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>139100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>133700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>139300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>125300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>136100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>139600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>143000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>135000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>137100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>138700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>133700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>126400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>130700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>156300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>127900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>125300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>126400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>130700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>127500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>132400</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E18" s="3">
         <v>51700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>39200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>44800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>46800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>47900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>21500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>50500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>48900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>43900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>22600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>29300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>34000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>43700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>34600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>37900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>35900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>40600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>36200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>32000</v>
-      </c>
-      <c r="W18" s="3">
-        <v>37300</v>
       </c>
       <c r="X18" s="3">
         <v>37300</v>
       </c>
       <c r="Y18" s="3">
+        <v>37300</v>
+      </c>
+      <c r="Z18" s="3">
         <v>32100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>24300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>30000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>20200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>19300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>11300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>20600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,8 +1782,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1758,7 +1792,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
         <v>100</v>
@@ -1767,188 +1801,194 @@
         <v>100</v>
       </c>
       <c r="H20" s="3">
+        <v>100</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>22000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>1900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>900</v>
-      </c>
-      <c r="P20" s="3">
-        <v>200</v>
       </c>
       <c r="Q20" s="3">
         <v>200</v>
       </c>
       <c r="R20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>500</v>
-      </c>
-      <c r="U20" s="3">
-        <v>700</v>
       </c>
       <c r="V20" s="3">
         <v>700</v>
       </c>
       <c r="W20" s="3">
+        <v>700</v>
+      </c>
+      <c r="X20" s="3">
         <v>1200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>61500</v>
+      </c>
+      <c r="E21" s="3">
         <v>63500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>44600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>47800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>49800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>51000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>54300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>53200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>49100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>29400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>36500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>39700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>48800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>39700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>41800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>40200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>45100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>40900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>36800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>42700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>41400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>36000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>28400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>33900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>23700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>22600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>14000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>24100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>14100</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E22" s="3">
         <v>1700</v>
-      </c>
-      <c r="E22" s="3">
-        <v>100</v>
       </c>
       <c r="F22" s="3">
         <v>100</v>
@@ -1957,10 +1997,10 @@
         <v>100</v>
       </c>
       <c r="H22" s="3">
+        <v>100</v>
+      </c>
+      <c r="I22" s="3">
         <v>300</v>
-      </c>
-      <c r="I22" s="3">
-        <v>100</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
@@ -1983,21 +2023,21 @@
       <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3" t="s">
+      <c r="Q22" s="3">
+        <v>100</v>
+      </c>
+      <c r="R22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
       <c r="V22" s="3">
         <v>0</v>
       </c>
@@ -2020,10 +2060,10 @@
         <v>0</v>
       </c>
       <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
         <v>400</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>100</v>
       </c>
       <c r="AE22" s="3">
         <v>100</v>
@@ -2034,198 +2074,207 @@
       <c r="AG22" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E23" s="3">
         <v>56500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>43200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>52400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>53000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>52900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>22400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>48100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>74600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>47100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>24400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>31300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>34700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>43800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>34800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>37300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>36000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>41000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>36900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>32800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>38500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>38700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>33600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>26000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>31600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>21000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>20200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>11800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>21400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E24" s="3">
         <v>12800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>11700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>14100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>14600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>13400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>19900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>12600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>9200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>8900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>11800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>10300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>9600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>9300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>10200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>9800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-7200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>10300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>9600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>6400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>7000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2368,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E26" s="3">
         <v>43700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>31500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>38300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>38400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>39400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>17200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>41300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>54700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>34500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>16000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>22100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>25800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>32100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>24500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>27800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>26700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>30800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>27100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>40000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>28200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>29100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>27500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>18400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>25200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>14000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>15100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>8900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>17900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E27" s="3">
         <v>43700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>31500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>38300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>38400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>39400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>17200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>41300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>54700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>34500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>16000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>22100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>25800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>32100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>24500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>27800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>26700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>30800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>27100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>40000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>28200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>29100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>27500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>18400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>25200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>14000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>15100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>8900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>17900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2662,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2636,8 +2697,8 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>8</v>
@@ -2648,8 +2709,8 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2676,31 +2737,34 @@
         <v>0</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-200</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-400</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>100</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-200</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-100</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-400</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-52400</v>
       </c>
     </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2858,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,8 +2956,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2898,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
         <v>-100</v>
@@ -2907,180 +2977,186 @@
         <v>-100</v>
       </c>
       <c r="H32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-22000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-1900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-900</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-200</v>
       </c>
       <c r="Q32" s="3">
         <v>-200</v>
       </c>
       <c r="R32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-500</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-700</v>
       </c>
       <c r="V32" s="3">
         <v>-700</v>
       </c>
       <c r="W32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="X32" s="3">
         <v>-1200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E33" s="3">
         <v>43700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>31500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>38300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>38400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>39400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>17200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>41300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>54700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>34500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>16000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>22100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>25800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>32100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>24500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>27800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>26600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>30800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>27100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>39900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>28200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>29100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>27500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>18200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>24800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>14100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>14900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>8800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>17500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3250,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E35" s="3">
         <v>43700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>31500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>38300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>38400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>39400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>17200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>41300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>54700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>34500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>16000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>22100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>25800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>32100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>24500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>27800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>26600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>30800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>27100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>39900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>28200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>29100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>27500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>18200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>24800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>14100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>14900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>8800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>17500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3489,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,343 +3525,353 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>172100</v>
+      </c>
+      <c r="E41" s="3">
         <v>132100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>109100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>238000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>127900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>125800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>118000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>165600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>140500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>89800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>109400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>147100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>148700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>190400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>320000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>266400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>87300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>86000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>105700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>58100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>91500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>37900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>108700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>47400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>51100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>38800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>32400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>32000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>33200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>24200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>465900</v>
+      </c>
+      <c r="E42" s="3">
         <v>458500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>459800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>483800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>546300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>515600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>485100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>429600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>428100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>420900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>399300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>375900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>366800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>307600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>174200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>209400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>389300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>361000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>300700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>305600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>250300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>243700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>185500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>234400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>228800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>200800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>196400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>156300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>151600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>158000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>156200</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>42400</v>
+      </c>
+      <c r="E43" s="3">
         <v>55700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>28100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>36100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>39800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>47200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>33900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>53300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>49200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>49300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>46000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>45300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>40800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>42900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>44700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>44400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>54300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>44200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>47600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>40300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>37100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>34100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>56400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>31200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>30500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>32400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>31300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>36500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>26900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>25300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E44" s="3">
         <v>3300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1200</v>
-      </c>
-      <c r="S44" s="3">
-        <v>600</v>
       </c>
       <c r="T44" s="3">
         <v>600</v>
@@ -3796,7 +3892,7 @@
         <v>600</v>
       </c>
       <c r="Z44" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AA44" s="3">
         <v>700</v>
@@ -3805,22 +3901,25 @@
         <v>700</v>
       </c>
       <c r="AC44" s="3">
+        <v>700</v>
+      </c>
+      <c r="AD44" s="3">
         <v>800</v>
-      </c>
-      <c r="AD44" s="3">
-        <v>900</v>
       </c>
       <c r="AE44" s="3">
         <v>900</v>
       </c>
       <c r="AF44" s="3">
+        <v>900</v>
+      </c>
+      <c r="AG44" s="3">
         <v>1000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3831,186 +3930,192 @@
         <v>200</v>
       </c>
       <c r="F45" s="3">
+        <v>200</v>
+      </c>
+      <c r="G45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>200</v>
       </c>
       <c r="I45" s="3">
         <v>200</v>
       </c>
       <c r="J45" s="3">
+        <v>200</v>
+      </c>
+      <c r="K45" s="3">
         <v>300</v>
-      </c>
-      <c r="K45" s="3">
-        <v>700</v>
       </c>
       <c r="L45" s="3">
         <v>700</v>
       </c>
       <c r="M45" s="3">
+        <v>700</v>
+      </c>
+      <c r="N45" s="3">
         <v>18500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>14600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>15800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>17600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>14300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>12600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>12200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>14600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>16000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>9200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>39300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>9800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>9500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>8500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>14400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>18100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>16900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>15300</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>721200</v>
+      </c>
+      <c r="E46" s="3">
         <v>686000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>640200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>773500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>732500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>706000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>655000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>669600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>643400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>585400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>575100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>582300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>571800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>556200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>554500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>537100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>549100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>506100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>467100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>416900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>394100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>332300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>360400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>353000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>320900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>282200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>269400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>240100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>230700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>225400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>210700</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4020,32 +4125,32 @@
       <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="3">
-        <v>1200</v>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G47" s="3">
         <v>1200</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
+      <c r="H47" s="3">
+        <v>1200</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>1000</v>
-      </c>
-      <c r="K47" s="3">
-        <v>1200</v>
       </c>
       <c r="L47" s="3">
         <v>1200</v>
       </c>
       <c r="M47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N47" s="3">
         <v>1900</v>
-      </c>
-      <c r="N47" s="3">
-        <v>1300</v>
       </c>
       <c r="O47" s="3">
         <v>1300</v>
@@ -4054,221 +4159,227 @@
         <v>1300</v>
       </c>
       <c r="Q47" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="R47" s="3">
         <v>1400</v>
       </c>
       <c r="S47" s="3">
+        <v>1400</v>
+      </c>
+      <c r="T47" s="3">
         <v>1500</v>
-      </c>
-      <c r="T47" s="3">
-        <v>1300</v>
       </c>
       <c r="U47" s="3">
         <v>1300</v>
       </c>
       <c r="V47" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="W47" s="3">
         <v>1200</v>
       </c>
       <c r="X47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Y47" s="3">
         <v>1100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>147300</v>
+      </c>
+      <c r="E48" s="3">
         <v>152000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>161000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>33800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>35500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>34900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>40500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>45600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>47400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>50000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>52200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>56600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>59400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>62500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>65000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>64600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>65600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>68100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>72500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>75900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>77200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>79400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>76400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>78700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>67600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>71800</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>30000</v>
       </c>
       <c r="AD48" s="3">
         <v>30000</v>
       </c>
       <c r="AE48" s="3">
+        <v>30000</v>
+      </c>
+      <c r="AF48" s="3">
         <v>30800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>32000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>33200</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>344600</v>
+      </c>
+      <c r="E49" s="3">
         <v>348700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>353000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>274100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>275200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>276300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>277400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>281100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>293200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>294900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>297100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>228400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>191500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>193100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>194800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>196800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>132200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>133000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>133800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>134700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>135500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>137100</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>95300</v>
       </c>
       <c r="Z49" s="3">
         <v>95300</v>
@@ -4294,8 +4405,11 @@
       <c r="AG49" s="3">
         <v>95300</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>95300</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4503,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,103 +4601,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7900</v>
+        <v>7700</v>
       </c>
       <c r="E52" s="3">
         <v>7900</v>
       </c>
       <c r="F52" s="3">
-        <v>5300</v>
+        <v>7900</v>
       </c>
       <c r="G52" s="3">
         <v>5300</v>
       </c>
       <c r="H52" s="3">
-        <v>6800</v>
+        <v>5300</v>
       </c>
       <c r="I52" s="3">
         <v>6800</v>
       </c>
       <c r="J52" s="3">
+        <v>6800</v>
+      </c>
+      <c r="K52" s="3">
         <v>4200</v>
-      </c>
-      <c r="K52" s="3">
-        <v>5700</v>
       </c>
       <c r="L52" s="3">
         <v>5700</v>
       </c>
       <c r="M52" s="3">
+        <v>5700</v>
+      </c>
+      <c r="N52" s="3">
         <v>31100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>30600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>32100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>30700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>31800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>36500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>38000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>41900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>46800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>55200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>47200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>56600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>65900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>70700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>77500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>80000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>86800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>93800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>99700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>101900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>105300</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4797,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1294400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1268500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1237000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1116800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1078200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1052000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1007300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1026000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1013700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>963000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>957400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>899200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>856100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>843800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>847400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>836400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>786400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>750400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>721500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>683800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>655100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>606500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>599100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>598800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>561800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>530200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>482500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>461400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>458800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>457300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>447100</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4933,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,136 +4969,140 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E57" s="3">
         <v>13400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>15400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>15200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>11500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>13300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>12900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>11900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>11500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>11000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>13100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>9200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>11300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>11700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E58" s="3">
         <v>10400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>13300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -5029,231 +5163,240 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>87700</v>
+      </c>
+      <c r="E59" s="3">
         <v>80700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>41700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>59700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>61900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>78000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>41200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>51300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>83000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>64800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>149900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>127100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>97800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>98200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>129400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>121800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>106200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>92500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>90600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>85600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>98500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>82700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>92300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>121100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>116100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>79500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>87900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>79000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>94600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>102400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>104200</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>168800</v>
+      </c>
+      <c r="E60" s="3">
         <v>154000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>132200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>141200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>134900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>142500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>111000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>139200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>160700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>135100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>163400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>140400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>110200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>110300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>140200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>134400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>117800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>103200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>103800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>98500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>110400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>92300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>103800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>132100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>128500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>92600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>97100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>91600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>105900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>114100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>112700</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>113900</v>
+      </c>
+      <c r="E61" s="3">
         <v>117300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>118300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>17300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>18400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>16700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>21300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>22900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>24400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>25800</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -5314,8 +5457,11 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5326,91 +5472,94 @@
         <v>27100</v>
       </c>
       <c r="F62" s="3">
+        <v>27100</v>
+      </c>
+      <c r="G62" s="3">
         <v>22800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>25400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>26700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>33500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>34300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>36200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>40900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>68100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>52600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>53100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>55100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>57100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>56600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>55000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>58800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>61800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>63600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>66000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>69100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>64000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>64700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>52100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>57200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>30200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>30100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>30000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>30300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5653,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5751,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +5849,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>309800</v>
+      </c>
+      <c r="E66" s="3">
         <v>298300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>277500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>181300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>178700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>185900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>165900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>196400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>221200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>201800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>231500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>193000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>163300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>165400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>197300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>191000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>172800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>162000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>165600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>162100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>176400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>161400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>167900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>196900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>180600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>149800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>127300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>121700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>135900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>144400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>150900</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5985,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6081,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6179,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6277,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6375,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>662900</v>
+      </c>
+      <c r="E72" s="3">
         <v>630500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>595700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>573000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>543600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>512600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>480600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>470800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>437000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>382300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>347800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>331900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>309800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>284100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>252000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>227500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>199700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>173100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>142300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>115300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>75300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>47200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>18100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-9400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-27700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-27100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-52900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-67000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-81900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-90600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-108100</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6571,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6669,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6767,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>984600</v>
+      </c>
+      <c r="E76" s="3">
         <v>970300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>959500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>935400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>899500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>866100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>841400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>829700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>792400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>761200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>725800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>706200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>692800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>678400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>650100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>645400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>613600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>588300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>555900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>521700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>478700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>445100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>431300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>401900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>381200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>380300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>355200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>339600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>322900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>313000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>296200</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6963,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E81" s="3">
         <v>43700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>31500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>38300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>38400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>39400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>17200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>41300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>54700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>34500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>16000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>22100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>25800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>32100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>24500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>27800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>26600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>30800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>27100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>39900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>28200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>29100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>27500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>18200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>24800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>14100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>14900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>8800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>17500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,34 +7202,35 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E83" s="3">
         <v>3000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>4900</v>
       </c>
       <c r="L83" s="3">
         <v>4900</v>
@@ -7040,25 +7239,25 @@
         <v>4900</v>
       </c>
       <c r="N83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="O83" s="3">
         <v>5100</v>
-      </c>
-      <c r="O83" s="3">
-        <v>4900</v>
       </c>
       <c r="P83" s="3">
         <v>4900</v>
       </c>
       <c r="Q83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="R83" s="3">
         <v>5000</v>
-      </c>
-      <c r="R83" s="3">
-        <v>3900</v>
       </c>
       <c r="S83" s="3">
         <v>3900</v>
       </c>
       <c r="T83" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="U83" s="3">
         <v>4000</v>
@@ -7067,40 +7266,43 @@
         <v>4000</v>
       </c>
       <c r="W83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="X83" s="3">
         <v>4200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2300</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>2200</v>
       </c>
       <c r="AB83" s="3">
         <v>2200</v>
       </c>
       <c r="AC83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AD83" s="3">
         <v>2300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>2400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>2100</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>2600</v>
       </c>
       <c r="AG83" s="3">
         <v>2600</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7396,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7494,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7592,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7690,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7788,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>78800</v>
+      </c>
+      <c r="E89" s="3">
         <v>65100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>17600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>51000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>38500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>54500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>13200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>32600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>61600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>40500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>52900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>32600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>22200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>46900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>61500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>38000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>44700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>42200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>28400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>60600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>48800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-12300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>32000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>40500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>12900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>38700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>11100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,103 +7924,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>-1400</v>
       </c>
       <c r="AF91" s="3">
         <v>-1400</v>
       </c>
       <c r="AG91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8118,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,103 +8216,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E94" s="3">
         <v>1200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-115100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>67400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-29300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-30800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-57300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-21400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-71000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-46100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-62700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-146900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>30000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>118600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-31700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-62600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>1600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-62000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-7600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-97900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>47000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-28200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-38400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-5500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>5300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,25 +8352,26 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E96" s="3">
         <v>9200</v>
-      </c>
-      <c r="E96" s="3">
-        <v>8500</v>
       </c>
       <c r="F96" s="3">
         <v>8500</v>
       </c>
       <c r="G96" s="3">
+        <v>8500</v>
+      </c>
+      <c r="H96" s="3">
         <v>7400</v>
-      </c>
-      <c r="H96" s="3">
-        <v>7200</v>
       </c>
       <c r="I96" s="3">
         <v>7200</v>
@@ -8145,14 +8379,14 @@
       <c r="J96" s="3">
         <v>7200</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>8</v>
+      <c r="K96" s="3">
+        <v>7200</v>
       </c>
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -8214,8 +8448,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8546,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8644,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,103 +8742,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-30300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-44400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-9600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-15900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-11000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-7400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-11700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-23300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-5100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-17600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1000</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8626,8 +8875,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -8687,101 +8936,107 @@
         <v>0</v>
       </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E102" s="3">
         <v>21900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-107100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>109900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>7800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-55100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>24100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>50700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-19600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-30400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-41700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-133500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>53600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>180300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-19700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>47600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-33400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>53600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-66800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>31300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>26000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>12300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>6400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>9000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>6100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PRDO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRDO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
   <si>
     <t>PRDO</t>
   </si>
@@ -656,455 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>211600</v>
+      </c>
+      <c r="E8" s="3">
         <v>211900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>209600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>213000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>176400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>169800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>166700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>168300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>147900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>179900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>186600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>195600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>176100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>168400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>167700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>183000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>159900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>174000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>175500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>183600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>171200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>169100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>176000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>171000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>158500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>155000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>156400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>157900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>145500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>145700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>142000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>148100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>143100</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E9" s="3">
         <v>43100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>44300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>42100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>31900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>26600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>26100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>27600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>27700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>31000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>30200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>31100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>31200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>30100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>27300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>28100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>25300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>26000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>28500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>29000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>28600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>27600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>28700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>26900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>24900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>25300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>25400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>26300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>25500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>27200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>30300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>26900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>168100</v>
+      </c>
+      <c r="E10" s="3">
         <v>168800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>165200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>170900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>144500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>143200</v>
-      </c>
-      <c r="I10" s="3">
-        <v>140700</v>
       </c>
       <c r="J10" s="3">
         <v>140700</v>
       </c>
       <c r="K10" s="3">
+        <v>140700</v>
+      </c>
+      <c r="L10" s="3">
         <v>120200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>148900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>156300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>164500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>144900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>138300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>140400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>154900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>134600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>148000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>147000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>154600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>142600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>141500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>147300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>144100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>133600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>129700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>131100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>131600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>120000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>118500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>111700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>121200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>114100</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1140,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1241,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1342,13 +1358,16 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>-1000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1356,45 +1375,45 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>3100</v>
-      </c>
-      <c r="H14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="H14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-16500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>7400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-21300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2800</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>200</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
@@ -1407,17 +1426,17 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>600</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
@@ -1428,11 +1447,11 @@
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AE14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>8</v>
@@ -1440,70 +1459,73 @@
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E15" s="3">
         <v>10000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>10100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>11800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5500</v>
-      </c>
-      <c r="H15" s="3">
-        <v>3100</v>
       </c>
       <c r="I15" s="3">
         <v>3100</v>
       </c>
       <c r="J15" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K15" s="3">
         <v>3000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>5100</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>4900</v>
       </c>
       <c r="R15" s="3">
         <v>4900</v>
       </c>
       <c r="S15" s="3">
+        <v>4900</v>
+      </c>
+      <c r="T15" s="3">
         <v>5000</v>
-      </c>
-      <c r="T15" s="3">
-        <v>3900</v>
       </c>
       <c r="U15" s="3">
         <v>3900</v>
       </c>
       <c r="V15" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="W15" s="3">
         <v>4000</v>
@@ -1512,40 +1534,43 @@
         <v>4000</v>
       </c>
       <c r="Y15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Z15" s="3">
         <v>4200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>2300</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>2200</v>
       </c>
       <c r="AD15" s="3">
         <v>2200</v>
       </c>
       <c r="AE15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AF15" s="3">
         <v>2300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>2400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>2100</v>
-      </c>
-      <c r="AH15" s="3">
-        <v>2600</v>
       </c>
       <c r="AI15" s="3">
         <v>2600</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>2600</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1578,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>169700</v>
+      </c>
+      <c r="E17" s="3">
         <v>160900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>158200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>161300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>137300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>125000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>119900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>120400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>126400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>129500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>137700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>151700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>153500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>139100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>133700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>139300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>125300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>136100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>139600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>143000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>135000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>137100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>138700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>133700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>126400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>130700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>156300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>127900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>125300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>126400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>130700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>127500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>132400</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E18" s="3">
         <v>51000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>51400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>51700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>39200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>44800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>46800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>47900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>21500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>50500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>48900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>43900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>22600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>29300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>34000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>43700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>34600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>37900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>35900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>40600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>36200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>32000</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>37300</v>
       </c>
       <c r="Z18" s="3">
         <v>37300</v>
       </c>
       <c r="AA18" s="3">
+        <v>37300</v>
+      </c>
+      <c r="AB18" s="3">
         <v>32100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>24300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>30000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>20200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>19300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>11300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>20600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1817,8 +1849,9 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1832,195 +1865,201 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="I20" s="3">
         <v>100</v>
       </c>
       <c r="J20" s="3">
+        <v>100</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>22000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>1900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>900</v>
-      </c>
-      <c r="R20" s="3">
-        <v>200</v>
       </c>
       <c r="S20" s="3">
         <v>200</v>
       </c>
       <c r="T20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>500</v>
-      </c>
-      <c r="W20" s="3">
-        <v>700</v>
       </c>
       <c r="X20" s="3">
         <v>700</v>
       </c>
       <c r="Y20" s="3">
+        <v>700</v>
+      </c>
+      <c r="Z20" s="3">
         <v>1200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>51600</v>
+      </c>
+      <c r="E21" s="3">
         <v>61000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>61500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>63500</v>
       </c>
-      <c r="G21" s="3">
-        <v>44600</v>
-      </c>
       <c r="H21" s="3">
+        <v>43500</v>
+      </c>
+      <c r="I21" s="3">
         <v>47800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>49800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>51000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>54300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>53200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>49100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>29400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>36500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>39700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>48800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>39700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>41800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>40200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>45100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>40900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>36800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>42700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>41400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>36000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>28400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>33900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>23700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>22600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>14000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>24100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>14100</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2031,10 +2070,10 @@
         <v>1600</v>
       </c>
       <c r="F22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G22" s="3">
         <v>1700</v>
-      </c>
-      <c r="G22" s="3">
-        <v>100</v>
       </c>
       <c r="H22" s="3">
         <v>100</v>
@@ -2043,10 +2082,10 @@
         <v>100</v>
       </c>
       <c r="J22" s="3">
+        <v>100</v>
+      </c>
+      <c r="K22" s="3">
         <v>300</v>
-      </c>
-      <c r="K22" s="3">
-        <v>100</v>
       </c>
       <c r="L22" s="3">
         <v>100</v>
@@ -2069,21 +2108,21 @@
       <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3" t="s">
+      <c r="S22" s="3">
+        <v>100</v>
+      </c>
+      <c r="T22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>100</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
       <c r="X22" s="3">
         <v>0</v>
       </c>
@@ -2106,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
         <v>400</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>100</v>
       </c>
       <c r="AG22" s="3">
         <v>100</v>
@@ -2120,210 +2159,219 @@
       <c r="AI22" s="3">
         <v>100</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>48100</v>
+      </c>
+      <c r="E23" s="3">
         <v>56000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>56200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>56500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>43200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>52400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>53000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>52900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>22400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>48100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>74600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>47100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>24400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>31300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>34700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>43800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>34800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>37300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>36000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>41000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>36900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>32800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>38500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>38700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>33600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>26000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>31600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>21000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>20200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>11800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>21400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E24" s="3">
         <v>16200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>15200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>12800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>11700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>14100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>13400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>19900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>12600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>8500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>9200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>8900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>11800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>10300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>9600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>9300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>10200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>9800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-7200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>10300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>9600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>6100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>7700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>6400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>7000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>5100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>3500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2423,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E26" s="3">
         <v>39900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>41000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>43700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>31500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>38300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>38400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>39400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>17200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>41300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>54700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>34500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>16000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>22100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>25800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>32100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>24500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>27800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>26700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>30800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>27100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>40000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>28200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>29100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>27500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>18400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>25200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>14000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>15100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>8900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>17900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E27" s="3">
         <v>39900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>41000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>43700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>31500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>38300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>38400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>39400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>17200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>41300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>54700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>34500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>16000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>22100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>25800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>32100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>24500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>27800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>26700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>30800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>27100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>40000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>28200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>29100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>27500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>18400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>25200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>14000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>15100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>8900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>17900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2726,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2764,8 +2824,8 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>8</v>
@@ -2776,8 +2836,8 @@
       <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -2804,31 +2864,34 @@
         <v>0</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-200</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-400</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>100</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-200</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-100</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-400</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-52400</v>
       </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2928,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3029,8 +3095,11 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3044,195 +3113,201 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-100</v>
+        <v>-1200</v>
       </c>
       <c r="I32" s="3">
         <v>-100</v>
       </c>
       <c r="J32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-22000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-1900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-900</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-200</v>
       </c>
       <c r="S32" s="3">
         <v>-200</v>
       </c>
       <c r="T32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-500</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-700</v>
       </c>
       <c r="X32" s="3">
         <v>-700</v>
       </c>
       <c r="Y32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E33" s="3">
         <v>39900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>41000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>43700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>31500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>38300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>38400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>39400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>17200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>41300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>54700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>34500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>16000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>22100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>25800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>32100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>24500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>27800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>26600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>30800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>27100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>39900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>28200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>29100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>27500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>18200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>24800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>14100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>14900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>8800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>17500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3332,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E35" s="3">
         <v>39900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>41000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>43700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>31500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>38300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>38400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>39400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>17200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>41300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>54700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>34500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>16000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>22100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>25800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>32100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>24500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>27800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>26600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>30800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>27100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>39900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>28200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>29100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>27500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>18200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>24800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>14100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>14900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>8800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>17500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3576,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3613,311 +3698,321 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E41" s="3">
         <v>159500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>172100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>132100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>109100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>238000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>127900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>125800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>118000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>165600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>140500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>89800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>109400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>147100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>148700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>190400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>320000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>266400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>87300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>86000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>105700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>58100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>91500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>37900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>108700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>47400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>51100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>38800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>32400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>32000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>33200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>24200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>511200</v>
+      </c>
+      <c r="E42" s="3">
         <v>487800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>465900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>458500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>459800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>483800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>546300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>515600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>485100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>429600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>428100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>420900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>399300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>375900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>366800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>307600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>174200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>209400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>389300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>361000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>300700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>305600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>250300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>243700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>185500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>234400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>228800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>200800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>196400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>156300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>151600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>158000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>156200</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E43" s="3">
         <v>47500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>42400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>55700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>28100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>36100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>39800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>47200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>33900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>53300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>49200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>49300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>46000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>45300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>40800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>42900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>44700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>44400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>54300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>44200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>47600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>40300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>37100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>34100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>56400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>31200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>30500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>32400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>31300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>36500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>26900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>25300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3925,55 +4020,55 @@
         <v>4000</v>
       </c>
       <c r="E44" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F44" s="3">
         <v>2600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1200</v>
-      </c>
-      <c r="U44" s="3">
-        <v>600</v>
       </c>
       <c r="V44" s="3">
         <v>600</v>
@@ -3994,7 +4089,7 @@
         <v>600</v>
       </c>
       <c r="AB44" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AC44" s="3">
         <v>700</v>
@@ -4003,22 +4098,25 @@
         <v>700</v>
       </c>
       <c r="AE44" s="3">
+        <v>700</v>
+      </c>
+      <c r="AF44" s="3">
         <v>800</v>
-      </c>
-      <c r="AF44" s="3">
-        <v>900</v>
       </c>
       <c r="AG44" s="3">
         <v>900</v>
       </c>
       <c r="AH44" s="3">
+        <v>900</v>
+      </c>
+      <c r="AI44" s="3">
         <v>1000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4035,192 +4133,198 @@
         <v>200</v>
       </c>
       <c r="H45" s="3">
+        <v>200</v>
+      </c>
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>500</v>
-      </c>
-      <c r="J45" s="3">
-        <v>200</v>
       </c>
       <c r="K45" s="3">
         <v>200</v>
       </c>
       <c r="L45" s="3">
+        <v>200</v>
+      </c>
+      <c r="M45" s="3">
         <v>300</v>
-      </c>
-      <c r="M45" s="3">
-        <v>700</v>
       </c>
       <c r="N45" s="3">
         <v>700</v>
       </c>
       <c r="O45" s="3">
+        <v>700</v>
+      </c>
+      <c r="P45" s="3">
         <v>18500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>14200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>13800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>14600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>15800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>17600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>14300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>12600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>12200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>14600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>16000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>9200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>39300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>9800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>9500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>8500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>14400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>18100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>16900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>15300</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>696900</v>
+      </c>
+      <c r="E46" s="3">
         <v>736200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>721200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>686000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>640200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>773500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>732500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>706000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>655000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>669600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>643400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>585400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>575100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>582300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>571800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>556200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>554500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>537100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>549100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>506100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>467100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>416900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>394100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>332300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>360400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>353000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>320900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>282200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>269400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>240100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>230700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>225400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>210700</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4236,32 +4340,32 @@
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
-        <v>1200</v>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I47" s="3">
         <v>1200</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
+      <c r="J47" s="3">
+        <v>1200</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3">
         <v>1000</v>
-      </c>
-      <c r="M47" s="3">
-        <v>1200</v>
       </c>
       <c r="N47" s="3">
         <v>1200</v>
       </c>
       <c r="O47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P47" s="3">
         <v>1900</v>
-      </c>
-      <c r="P47" s="3">
-        <v>1300</v>
       </c>
       <c r="Q47" s="3">
         <v>1300</v>
@@ -4270,233 +4374,239 @@
         <v>1300</v>
       </c>
       <c r="S47" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="T47" s="3">
         <v>1400</v>
       </c>
       <c r="U47" s="3">
+        <v>1400</v>
+      </c>
+      <c r="V47" s="3">
         <v>1500</v>
-      </c>
-      <c r="V47" s="3">
-        <v>1300</v>
       </c>
       <c r="W47" s="3">
         <v>1300</v>
       </c>
       <c r="X47" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="Y47" s="3">
         <v>1200</v>
       </c>
       <c r="Z47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AA47" s="3">
         <v>1100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>136900</v>
+      </c>
+      <c r="E48" s="3">
         <v>141800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>147300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>152000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>161000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>33800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>35500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>34900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>40500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>45600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>47400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>50000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>52200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>56600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>59400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>62500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>65000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>64600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>65600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>68100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>72500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>75900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>77200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>79400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>76400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>78700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>67600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>71800</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>30000</v>
       </c>
       <c r="AF48" s="3">
         <v>30000</v>
       </c>
       <c r="AG48" s="3">
+        <v>30000</v>
+      </c>
+      <c r="AH48" s="3">
         <v>30800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>32000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>33200</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>343600</v>
+      </c>
+      <c r="E49" s="3">
         <v>340300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>344600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>348700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>353000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>274100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>275200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>276300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>277400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>281100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>293200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>294900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>297100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>228400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>191500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>193100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>194800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>196800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>132200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>133000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>133800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>134700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>135500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>137100</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>95300</v>
       </c>
       <c r="AB49" s="3">
         <v>95300</v>
@@ -4522,8 +4632,11 @@
       <c r="AI49" s="3">
         <v>95300</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>95300</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4623,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4724,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E52" s="3">
         <v>7500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7700</v>
-      </c>
-      <c r="F52" s="3">
-        <v>7900</v>
       </c>
       <c r="G52" s="3">
         <v>7900</v>
       </c>
       <c r="H52" s="3">
-        <v>5300</v>
+        <v>7900</v>
       </c>
       <c r="I52" s="3">
         <v>5300</v>
       </c>
       <c r="J52" s="3">
-        <v>6800</v>
+        <v>5300</v>
       </c>
       <c r="K52" s="3">
         <v>6800</v>
       </c>
       <c r="L52" s="3">
+        <v>6800</v>
+      </c>
+      <c r="M52" s="3">
         <v>4200</v>
-      </c>
-      <c r="M52" s="3">
-        <v>5700</v>
       </c>
       <c r="N52" s="3">
         <v>5700</v>
       </c>
       <c r="O52" s="3">
+        <v>5700</v>
+      </c>
+      <c r="P52" s="3">
         <v>31100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>30600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>32100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>30700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>31800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>36500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>38000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>41900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>46800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>55200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>47200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>56600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>65900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>70700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>77500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>80000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>86800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>93800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>99700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>101900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>105300</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4926,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1247700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1299400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1294400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1268500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1237000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1116800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1078200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1052000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1007300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1026000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1013700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>963000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>957400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>899200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>856100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>843800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>847400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>836400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>786400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>750400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>721500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>683800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>655100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>606500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>599100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>598800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>561800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>530200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>482500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>461400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>458800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>457300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>447100</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5064,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5101,148 +5230,152 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E57" s="3">
         <v>20200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>15400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>15200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>12700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>10800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>13300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>12900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>11900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>9600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>11500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>11000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>13100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>12600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>11300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>11700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E58" s="3">
         <v>11100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6000</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -5303,249 +5436,258 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E59" s="3">
         <v>70500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>87700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>80700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>41700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>59700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>61900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>78000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>41200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>51300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>83000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>64800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>149900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>127100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>97800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>98200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>129400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>121800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>106200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>92500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>90600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>85600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>98500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>82700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>92300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>121100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>116100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>79500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>87900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>79000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>94600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>102400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>104200</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>137800</v>
+      </c>
+      <c r="E60" s="3">
         <v>164600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>168800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>154000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>132200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>141200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>134900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>142500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>111000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>139200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>160700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>135100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>163400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>140400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>110200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>110300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>140200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>134400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>117800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>103200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>103800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>98500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>110400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>92300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>103800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>132100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>128500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>92600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>97100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>91600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>105900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>114100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>112700</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>106800</v>
+      </c>
+      <c r="E61" s="3">
         <v>110400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>113900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>117300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>118300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>17300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>18400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>16700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>21300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>22900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>24400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>25800</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -5606,16 +5748,19 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E62" s="3">
         <v>26500</v>
-      </c>
-      <c r="E62" s="3">
-        <v>27100</v>
       </c>
       <c r="F62" s="3">
         <v>27100</v>
@@ -5624,91 +5769,94 @@
         <v>27100</v>
       </c>
       <c r="H62" s="3">
+        <v>27100</v>
+      </c>
+      <c r="I62" s="3">
         <v>22800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>25400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>26700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>33500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>34300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>36200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>40900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>68100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>52600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>53100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>55100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>57100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>56600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>55000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>58800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>61800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>63600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>66000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>69100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>64000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>64700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>52100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>57200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>30200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>30100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>30000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>30300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5808,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5909,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6010,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>275300</v>
+      </c>
+      <c r="E66" s="3">
         <v>301500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>309800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>298300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>277500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>181300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>178700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>185900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>165900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>196400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>221200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>201800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>231500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>193000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>163300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>165400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>197300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>191000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>172800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>162000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>165600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>162100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>176400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>161400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>167900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>196900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>180600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>149800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>127300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>121700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>135900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>144400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>150900</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6148,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6249,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6350,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6451,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6552,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>718400</v>
+      </c>
+      <c r="E72" s="3">
         <v>692800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>662900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>630500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>595700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>573000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>543600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>512600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>480600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>470800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>437000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>382300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>347800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>331900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>309800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>284100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>252000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>227500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>199700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>173100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>142300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>115300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>75300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>47200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>18100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-9400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-27700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-27100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-52900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-67000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-81900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-90600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-108100</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6754,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6855,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6956,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>972400</v>
+      </c>
+      <c r="E76" s="3">
         <v>997900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>984600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>970300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>959500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>935400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>899500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>866100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>841400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>829700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>792400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>761200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>725800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>706200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>692800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>678400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>650100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>645400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>613600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>588300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>555900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>521700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>478700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>445100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>431300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>401900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>381200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>380300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>355200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>339600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>322900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>313000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>296200</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7158,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E81" s="3">
         <v>39900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>41000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>43700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>31500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>38300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>38400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>39400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>17200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>41300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>54700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>34500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>16000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>22100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>25800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>32100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>24500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>27800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>26600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>30800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>27100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>39900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>28200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>29100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>27500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>18200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>24800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>14100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>14900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>8800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>17500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7402,40 +7599,41 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3100</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
         <v>3100</v>
       </c>
       <c r="F83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G83" s="3">
         <v>3000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5100</v>
-      </c>
-      <c r="M83" s="3">
-        <v>4900</v>
       </c>
       <c r="N83" s="3">
         <v>4900</v>
@@ -7444,25 +7642,25 @@
         <v>4900</v>
       </c>
       <c r="P83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="Q83" s="3">
         <v>5100</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>4900</v>
       </c>
       <c r="R83" s="3">
         <v>4900</v>
       </c>
       <c r="S83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="T83" s="3">
         <v>5000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>3900</v>
       </c>
       <c r="U83" s="3">
         <v>3900</v>
       </c>
       <c r="V83" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="W83" s="3">
         <v>4000</v>
@@ -7471,40 +7669,43 @@
         <v>4000</v>
       </c>
       <c r="Y83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Z83" s="3">
         <v>4200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>2300</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>2200</v>
       </c>
       <c r="AD83" s="3">
         <v>2200</v>
       </c>
       <c r="AE83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AF83" s="3">
         <v>2300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>2400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>2100</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>2600</v>
       </c>
       <c r="AI83" s="3">
         <v>2600</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>2600</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7604,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7705,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7806,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7907,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8008,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E89" s="3">
         <v>41200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>78800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>65100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>17600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>51000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>38500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>54500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>13200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>32600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>61600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>40500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>52900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>32600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>22200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>46900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>61500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>38000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>44700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>42200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>28400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>60600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>48800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-12300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>32000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>40500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>12900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>38700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>11100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8146,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>-1400</v>
       </c>
       <c r="AH91" s="3">
         <v>-1400</v>
       </c>
       <c r="AI91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8348,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8449,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-23800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-22600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-115100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>67400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-29300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-30800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-57300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-21400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-71000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-46100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-62700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-146900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>30000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>118600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-31700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-62600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>1600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-62000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-97900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>47000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-28200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-38400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-5500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>5300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8587,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E96" s="3">
         <v>9700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>8500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>9200</v>
-      </c>
-      <c r="G96" s="3">
-        <v>8500</v>
       </c>
       <c r="H96" s="3">
         <v>8500</v>
       </c>
       <c r="I96" s="3">
+        <v>8500</v>
+      </c>
+      <c r="J96" s="3">
         <v>7400</v>
-      </c>
-      <c r="J96" s="3">
-        <v>7200</v>
       </c>
       <c r="K96" s="3">
         <v>7200</v>
@@ -8619,14 +8852,14 @@
       <c r="L96" s="3">
         <v>7200</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>8</v>
+      <c r="M96" s="3">
+        <v>7200</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -8688,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8789,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8890,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8991,109 +9233,115 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-64800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-31600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-30300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-44400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-9600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-8500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-15900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-11000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-11700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-8800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-23300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-5100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-17600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1000</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9130,8 +9378,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -9191,107 +9439,113 @@
         <v>0</v>
       </c>
       <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-48500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-12900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>40000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>21900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-107100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>109900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-55100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>24100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>50700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-19600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-30400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-41700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-133500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>53600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>180300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-19700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>47600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-33400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>53600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-66800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>31300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>26000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>12300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>6400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>9000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>6100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PRDO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRDO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
   <si>
     <t>PRDO</t>
   </si>
@@ -656,467 +656,480 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>221700</v>
+      </c>
+      <c r="E8" s="3">
         <v>211600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>211900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>209600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>213000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>176400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>169800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>166700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>168300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>147900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>179900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>186600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>195600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>176100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>168400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>167700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>183000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>159900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>174000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>175500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>183600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>171200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>169100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>176000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>171000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>158500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>155000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>156400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>157900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>145500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>145700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>142000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>148100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>143100</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E9" s="3">
         <v>43500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>43100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>44300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>42100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>31900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>26600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>26100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>27600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>27700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>31000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>30200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>31100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>31200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>30100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>27300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>28100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>25300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>26000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>28500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>29000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>28600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>27600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>28700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>26900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>24900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>25300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>25400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>26300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>25500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>27200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>30300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>26900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>180700</v>
+      </c>
+      <c r="E10" s="3">
         <v>168100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>168800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>165200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>170900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>144500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>143200</v>
-      </c>
-      <c r="J10" s="3">
-        <v>140700</v>
       </c>
       <c r="K10" s="3">
         <v>140700</v>
       </c>
       <c r="L10" s="3">
+        <v>140700</v>
+      </c>
+      <c r="M10" s="3">
         <v>120200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>148900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>156300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>164500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>144900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>138300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>140400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>154900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>134600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>148000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>147000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>154600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>142600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>141500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>147300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>144100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>133600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>129700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>131100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>131600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>120000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>118500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>111700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>121200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>114100</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1166,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1257,8 +1271,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,16 +1378,19 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1000</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1378,45 +1398,45 @@
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>2000</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-16500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>7400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-21300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2800</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>200</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
@@ -1429,17 +1449,17 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3" t="s">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>600</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
@@ -1450,11 +1470,11 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3" t="s">
+      <c r="AF14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>8</v>
@@ -1462,73 +1482,76 @@
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E15" s="3">
         <v>9700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>10000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>10100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5500</v>
-      </c>
-      <c r="I15" s="3">
-        <v>3100</v>
       </c>
       <c r="J15" s="3">
         <v>3100</v>
       </c>
       <c r="K15" s="3">
+        <v>3100</v>
+      </c>
+      <c r="L15" s="3">
         <v>3000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>5100</v>
-      </c>
-      <c r="R15" s="3">
-        <v>4900</v>
       </c>
       <c r="S15" s="3">
         <v>4900</v>
       </c>
       <c r="T15" s="3">
+        <v>4900</v>
+      </c>
+      <c r="U15" s="3">
         <v>5000</v>
-      </c>
-      <c r="U15" s="3">
-        <v>3900</v>
       </c>
       <c r="V15" s="3">
         <v>3900</v>
       </c>
       <c r="W15" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="X15" s="3">
         <v>4000</v>
@@ -1537,40 +1560,43 @@
         <v>4000</v>
       </c>
       <c r="Z15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AA15" s="3">
         <v>4200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>2400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>2300</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>2200</v>
       </c>
       <c r="AE15" s="3">
         <v>2200</v>
       </c>
       <c r="AF15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AG15" s="3">
         <v>2300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>2400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>2100</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>2600</v>
       </c>
       <c r="AJ15" s="3">
         <v>2600</v>
       </c>
+      <c r="AK15" s="3">
+        <v>2600</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1630,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>158600</v>
+      </c>
+      <c r="E17" s="3">
         <v>169700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>160900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>158200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>161300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>137300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>125000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>119900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>120400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>126400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>129500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>137700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>151700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>153500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>139100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>133700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>139300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>125300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>136100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>139600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>143000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>135000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>137100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>138700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>133700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>126400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>130700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>156300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>127900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>125300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>126400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>130700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>127500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>132400</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>63100</v>
+      </c>
+      <c r="E18" s="3">
         <v>41900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>51000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>51400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>51700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>39200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>44800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>46800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>47900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>21500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>50500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>48900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>43900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>22600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>29300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>34000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>43700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>34600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>37900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>35900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>40600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>36200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>32000</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>37300</v>
       </c>
       <c r="AA18" s="3">
         <v>37300</v>
       </c>
       <c r="AB18" s="3">
+        <v>37300</v>
+      </c>
+      <c r="AC18" s="3">
         <v>32100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>24300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>30000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>20200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>19300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>11300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>20600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,8 +1883,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1868,203 +1902,209 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>1200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>100</v>
       </c>
       <c r="J20" s="3">
         <v>100</v>
       </c>
       <c r="K20" s="3">
+        <v>100</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>22000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>1900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>900</v>
-      </c>
-      <c r="S20" s="3">
-        <v>200</v>
       </c>
       <c r="T20" s="3">
         <v>200</v>
       </c>
       <c r="U20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>500</v>
-      </c>
-      <c r="X20" s="3">
-        <v>700</v>
       </c>
       <c r="Y20" s="3">
         <v>700</v>
       </c>
       <c r="Z20" s="3">
+        <v>700</v>
+      </c>
+      <c r="AA20" s="3">
         <v>1200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>72500</v>
+      </c>
+      <c r="E21" s="3">
         <v>51600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>61000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>61500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>63500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>43500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>47800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>49800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>51000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>54300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>53200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>49100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>29400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>36500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>39700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>48800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>39700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>41800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>40200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>45100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>40900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>36800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>42700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>41400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>36000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>28400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>33900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>23700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>22600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>14000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>24100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>14100</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="E22" s="3">
         <v>1600</v>
@@ -2073,10 +2113,10 @@
         <v>1600</v>
       </c>
       <c r="G22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H22" s="3">
         <v>1700</v>
-      </c>
-      <c r="H22" s="3">
-        <v>100</v>
       </c>
       <c r="I22" s="3">
         <v>100</v>
@@ -2085,10 +2125,10 @@
         <v>100</v>
       </c>
       <c r="K22" s="3">
+        <v>100</v>
+      </c>
+      <c r="L22" s="3">
         <v>300</v>
-      </c>
-      <c r="L22" s="3">
-        <v>100</v>
       </c>
       <c r="M22" s="3">
         <v>100</v>
@@ -2111,21 +2151,21 @@
       <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3" t="s">
+      <c r="T22" s="3">
+        <v>100</v>
+      </c>
+      <c r="U22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>100</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
       <c r="Y22" s="3">
         <v>0</v>
       </c>
@@ -2148,10 +2188,10 @@
         <v>0</v>
       </c>
       <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
         <v>400</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>100</v>
       </c>
       <c r="AH22" s="3">
         <v>100</v>
@@ -2162,216 +2202,225 @@
       <c r="AJ22" s="3">
         <v>100</v>
       </c>
+      <c r="AK22" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>68100</v>
+      </c>
+      <c r="E23" s="3">
         <v>48100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>56000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>56200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>56500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>43200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>52400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>53000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>52900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>22400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>48100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>74600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>47100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>24400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>31300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>34700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>43800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>34800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>37300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>36000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>41000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>36900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>32800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>38500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>38700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>33600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>26000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>31600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>21000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>20200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>11800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>21400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E24" s="3">
         <v>12700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>16200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>15200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>12800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>11700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>14600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>13400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>19900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>12600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>8500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>8900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>11800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>10300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>9600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>9300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>10200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>9800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-7200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>10300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>9600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>6100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>7700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>6400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>7000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>5100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2523,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E26" s="3">
         <v>35300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>39900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>41000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>43700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>31500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>38300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>38400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>39400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>17200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>41300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>54700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>34500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>16000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>22100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>25800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>32100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>24500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>27800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>26700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>30800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>27100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>40000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>28200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>29100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>27500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>18400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>25200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>14000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>15100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>8900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>17900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E27" s="3">
         <v>35300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>39900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>41000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>43700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>31500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>38300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>38400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>39400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>17200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>41300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>54700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>34500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>16000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>22100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>25800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>32100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>24500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>27800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>26700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>30800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>27100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>40000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>28200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>29100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>27500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>18400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>25200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>14000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>15100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>8900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>17900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2844,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2827,8 +2888,8 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>8</v>
@@ -2839,8 +2900,8 @@
       <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -2867,31 +2928,34 @@
         <v>0</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-200</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-400</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>100</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-200</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-100</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-52400</v>
       </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3058,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,8 +3165,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3116,198 +3186,204 @@
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-1200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-100</v>
       </c>
       <c r="J32" s="3">
         <v>-100</v>
       </c>
       <c r="K32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-22000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-900</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-200</v>
       </c>
       <c r="T32" s="3">
         <v>-200</v>
       </c>
       <c r="U32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-500</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-700</v>
       </c>
       <c r="Y32" s="3">
         <v>-700</v>
       </c>
       <c r="Z32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E33" s="3">
         <v>35300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>39900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>41000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>43700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>31500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>38300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>38400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>39400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>17200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>41300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>54700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>34500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>16000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>22100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>25800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>32100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>24500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>27800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>26600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>30800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>27100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>39900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>28200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>29100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>27500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>18200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>24800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>14100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>14900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>8800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>17500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3486,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E35" s="3">
         <v>35300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>39900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>41000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>43700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>31500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>38300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>38400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>39400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>17200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>41300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>54700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>34500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>16000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>22100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>25800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>32100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>24500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>27800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>26600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>30800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>27100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>39900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>28200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>29100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>27500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>18200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>24800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>14100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>14900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>8800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>17500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3746,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,379 +3785,389 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>164300</v>
+      </c>
+      <c r="E41" s="3">
         <v>111000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>159500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>172100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>132100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>109100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>238000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>127900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>125800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>118000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>165600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>140500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>89800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>109400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>147100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>148700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>190400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>320000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>266400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>87300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>86000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>105700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>58100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>91500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>37900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>108700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>47400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>51100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>38800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>32400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>32000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>33200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>24200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>514800</v>
+      </c>
+      <c r="E42" s="3">
         <v>511200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>487800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>465900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>458500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>459800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>483800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>546300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>515600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>485100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>429600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>428100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>420900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>399300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>375900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>366800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>307600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>174200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>209400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>389300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>361000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>300700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>305600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>250300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>243700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>185500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>234400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>228800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>200800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>196400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>156300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>151600</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>158000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>156200</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>46500</v>
+      </c>
+      <c r="E43" s="3">
         <v>32200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>47500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>42400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>55700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>28100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>36100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>39800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>47200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>33900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>53300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>49200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>49300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>46000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>45300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>40800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>42900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>44700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>44400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>54300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>44200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>47600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>40300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>37100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>34100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>56400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>31200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>30500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>32400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>31300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>36500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>26900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>25300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4000</v>
+        <v>3300</v>
       </c>
       <c r="E44" s="3">
         <v>4000</v>
       </c>
       <c r="F44" s="3">
+        <v>4000</v>
+      </c>
+      <c r="G44" s="3">
         <v>2600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1200</v>
-      </c>
-      <c r="V44" s="3">
-        <v>600</v>
       </c>
       <c r="W44" s="3">
         <v>600</v>
@@ -4092,7 +4188,7 @@
         <v>600</v>
       </c>
       <c r="AC44" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AD44" s="3">
         <v>700</v>
@@ -4101,27 +4197,30 @@
         <v>700</v>
       </c>
       <c r="AF44" s="3">
+        <v>700</v>
+      </c>
+      <c r="AG44" s="3">
         <v>800</v>
-      </c>
-      <c r="AG44" s="3">
-        <v>900</v>
       </c>
       <c r="AH44" s="3">
         <v>900</v>
       </c>
       <c r="AI44" s="3">
+        <v>900</v>
+      </c>
+      <c r="AJ44" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E45" s="3">
         <v>200</v>
@@ -4136,195 +4235,201 @@
         <v>200</v>
       </c>
       <c r="I45" s="3">
+        <v>200</v>
+      </c>
+      <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>500</v>
-      </c>
-      <c r="K45" s="3">
-        <v>200</v>
       </c>
       <c r="L45" s="3">
         <v>200</v>
       </c>
       <c r="M45" s="3">
+        <v>200</v>
+      </c>
+      <c r="N45" s="3">
         <v>300</v>
-      </c>
-      <c r="N45" s="3">
-        <v>700</v>
       </c>
       <c r="O45" s="3">
         <v>700</v>
       </c>
       <c r="P45" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q45" s="3">
         <v>18500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>12000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>14200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>13800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>14600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>15800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>17600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>14300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>12600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>12200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>14600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>16000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>9200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>39300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>9800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>9500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>8500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>14400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>18100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>16900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>15300</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>747300</v>
+      </c>
+      <c r="E46" s="3">
         <v>696900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>736200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>721200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>686000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>640200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>773500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>732500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>706000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>655000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>669600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>643400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>585400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>575100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>582300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>571800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>556200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>554500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>537100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>549100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>506100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>467100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>416900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>394100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>332300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>360400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>353000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>320900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>282200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>269400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>240100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>230700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>225400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>210700</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4343,32 +4448,32 @@
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3">
-        <v>1200</v>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J47" s="3">
         <v>1200</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
+      <c r="K47" s="3">
+        <v>1200</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3">
         <v>1000</v>
-      </c>
-      <c r="N47" s="3">
-        <v>1200</v>
       </c>
       <c r="O47" s="3">
         <v>1200</v>
       </c>
       <c r="P47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Q47" s="3">
         <v>1900</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>1300</v>
       </c>
       <c r="R47" s="3">
         <v>1300</v>
@@ -4377,239 +4482,245 @@
         <v>1300</v>
       </c>
       <c r="T47" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="U47" s="3">
         <v>1400</v>
       </c>
       <c r="V47" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W47" s="3">
         <v>1500</v>
-      </c>
-      <c r="W47" s="3">
-        <v>1300</v>
       </c>
       <c r="X47" s="3">
         <v>1300</v>
       </c>
       <c r="Y47" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="Z47" s="3">
         <v>1200</v>
       </c>
       <c r="AA47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AB47" s="3">
         <v>1100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>131500</v>
+      </c>
+      <c r="E48" s="3">
         <v>136900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>141800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>147300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>152000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>161000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>33800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>35500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>34900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>40500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>45600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>47400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>50000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>52200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>56600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>59400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>62500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>65000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>64600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>65600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>68100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>72500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>75900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>77200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>79400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>76400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>78700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>67600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>71800</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>30000</v>
       </c>
       <c r="AG48" s="3">
         <v>30000</v>
       </c>
       <c r="AH48" s="3">
+        <v>30000</v>
+      </c>
+      <c r="AI48" s="3">
         <v>30800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>32000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>33200</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>339500</v>
+      </c>
+      <c r="E49" s="3">
         <v>343600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>340300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>344600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>348700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>353000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>274100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>275200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>276300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>277400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>281100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>293200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>294900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>297100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>228400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>191500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>193100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>194800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>196800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>132200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>133000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>133800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>134700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>135500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>137100</v>
-      </c>
-      <c r="AB49" s="3">
-        <v>95300</v>
       </c>
       <c r="AC49" s="3">
         <v>95300</v>
@@ -4635,8 +4746,11 @@
       <c r="AJ49" s="3">
         <v>95300</v>
       </c>
+      <c r="AK49" s="3">
+        <v>95300</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4853,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,8 +4960,11 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4852,103 +4972,106 @@
         <v>8100</v>
       </c>
       <c r="E52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F52" s="3">
         <v>7500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7700</v>
-      </c>
-      <c r="G52" s="3">
-        <v>7900</v>
       </c>
       <c r="H52" s="3">
         <v>7900</v>
       </c>
       <c r="I52" s="3">
-        <v>5300</v>
+        <v>7900</v>
       </c>
       <c r="J52" s="3">
         <v>5300</v>
       </c>
       <c r="K52" s="3">
-        <v>6800</v>
+        <v>5300</v>
       </c>
       <c r="L52" s="3">
         <v>6800</v>
       </c>
       <c r="M52" s="3">
+        <v>6800</v>
+      </c>
+      <c r="N52" s="3">
         <v>4200</v>
-      </c>
-      <c r="N52" s="3">
-        <v>5700</v>
       </c>
       <c r="O52" s="3">
         <v>5700</v>
       </c>
       <c r="P52" s="3">
+        <v>5700</v>
+      </c>
+      <c r="Q52" s="3">
         <v>31100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>30600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>32100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>30700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>31800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>36500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>38000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>41900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>46800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>55200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>47200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>56600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>65900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>70700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>77500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>80000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>86800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>93800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>99700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>101900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>105300</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5174,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1288800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1247700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1299400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1294400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1268500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1237000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1116800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1078200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1052000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1007300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1026000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1013700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>963000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>957400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>899200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>856100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>843800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>847400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>836400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>786400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>750400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>721500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>683800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>655100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>606500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>599100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>598800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>561800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>530200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>482500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>461400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>458800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>457300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>447100</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5322,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,154 +5361,158 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E57" s="3">
         <v>14300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>20200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>16600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>12800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>15400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>15200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>13300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>12100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>12700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>11500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>13300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>12900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>11900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>9600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>11500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>11000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>13100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>12600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>11300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>11700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E58" s="3">
         <v>11500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>13300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6000</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -5439,258 +5573,267 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>72000</v>
+      </c>
+      <c r="E59" s="3">
         <v>43500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>70500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>87700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>80700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>41700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>59700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>61900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>78000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>41200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>51300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>83000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>64800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>149900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>127100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>97800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>98200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>129400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>121800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>106200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>92500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>90600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>85600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>98500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>82700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>92300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>121100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>116100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>79500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>87900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>79000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>94600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>102400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>104200</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>155200</v>
+      </c>
+      <c r="E60" s="3">
         <v>137800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>164600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>168800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>154000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>132200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>141200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>134900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>142500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>111000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>139200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>160700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>135100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>163400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>140400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>110200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>110300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>140200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>134400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>117800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>103200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>103800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>98500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>110400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>92300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>103800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>132100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>128500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>92600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>97100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>91600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>105900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>114100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>112700</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>103200</v>
+      </c>
+      <c r="E61" s="3">
         <v>106800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>110400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>113900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>117300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>118300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>17300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>18400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>16700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>21300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>22900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>24400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>25800</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -5751,19 +5894,22 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E62" s="3">
         <v>30700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>26500</v>
-      </c>
-      <c r="F62" s="3">
-        <v>27100</v>
       </c>
       <c r="G62" s="3">
         <v>27100</v>
@@ -5772,91 +5918,94 @@
         <v>27100</v>
       </c>
       <c r="I62" s="3">
+        <v>27100</v>
+      </c>
+      <c r="J62" s="3">
         <v>22800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>25400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>26700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>33500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>34300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>36200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>40900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>68100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>52600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>53100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>55100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>57100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>56600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>55000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>58800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>61800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>63600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>66000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>69100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>64000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>64700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>52100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>57200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>30200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>30100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>30000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>30300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6108,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6215,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6322,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>288900</v>
+      </c>
+      <c r="E66" s="3">
         <v>275300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>301500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>309800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>298300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>277500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>181300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>178700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>185900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>165900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>196400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>221200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>201800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>231500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>193000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>163300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>165400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>197300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>191000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>172800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>162000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>165600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>162100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>176400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>161400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>167900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>196900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>180600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>149800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>127300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>121700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>135900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>144400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>150900</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6470,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6575,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6682,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6789,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6896,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>762700</v>
+      </c>
+      <c r="E72" s="3">
         <v>718400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>692800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>662900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>630500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>595700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>573000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>543600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>512600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>480600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>470800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>437000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>382300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>347800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>331900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>309800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>284100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>252000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>227500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>199700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>173100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>142300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>115300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>75300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>47200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>18100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-9400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-27700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-27100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-52900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-67000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-81900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-90600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-108100</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7110,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7217,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7324,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>999900</v>
+      </c>
+      <c r="E76" s="3">
         <v>972400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>997900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>984600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>970300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>959500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>935400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>899500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>866100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>841400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>829700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>792400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>761200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>725800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>706200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>692800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>678400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>650100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>645400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>613600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>588300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>555900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>521700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>478700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>445100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>431300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>401900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>381200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>380300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>355200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>339600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>322900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>313000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>296200</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7538,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E81" s="3">
         <v>35300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>39900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>41000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>43700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>31500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>38300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>38400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>39400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>17200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>41300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>54700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>34500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>16000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>22100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>25800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>32100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>24500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>27800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>26600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>30800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>27100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>39900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>28200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>29100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>27500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>18200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>24800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>14100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>14900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>8800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>17500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-44400</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,43 +7798,44 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>11800</v>
       </c>
       <c r="E83" s="3">
-        <v>3100</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>3100</v>
       </c>
       <c r="G83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H83" s="3">
         <v>3000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5100</v>
-      </c>
-      <c r="N83" s="3">
-        <v>4900</v>
       </c>
       <c r="O83" s="3">
         <v>4900</v>
@@ -7645,25 +7844,25 @@
         <v>4900</v>
       </c>
       <c r="Q83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="R83" s="3">
         <v>5100</v>
-      </c>
-      <c r="R83" s="3">
-        <v>4900</v>
       </c>
       <c r="S83" s="3">
         <v>4900</v>
       </c>
       <c r="T83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="U83" s="3">
         <v>5000</v>
-      </c>
-      <c r="U83" s="3">
-        <v>3900</v>
       </c>
       <c r="V83" s="3">
         <v>3900</v>
       </c>
       <c r="W83" s="3">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="X83" s="3">
         <v>4000</v>
@@ -7672,40 +7871,43 @@
         <v>4000</v>
       </c>
       <c r="Z83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AA83" s="3">
         <v>4200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>2400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2300</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>2200</v>
       </c>
       <c r="AE83" s="3">
         <v>2200</v>
       </c>
       <c r="AF83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AG83" s="3">
         <v>2300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>2400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>2100</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>2600</v>
       </c>
       <c r="AJ83" s="3">
         <v>2600</v>
       </c>
+      <c r="AK83" s="3">
+        <v>2600</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8010,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8117,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8224,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8331,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8438,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>69400</v>
+      </c>
+      <c r="E89" s="3">
         <v>40100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>41200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>78800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>65100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>17600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>51000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>38500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>54500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>13200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>32600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>61600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>40500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>52900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>32600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>22200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>46900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>61500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>38000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>44700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>42200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>28400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>60600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>48800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-12300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>32000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>40500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>12900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>38700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>11100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8586,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="AH91" s="3">
-        <v>-1400</v>
       </c>
       <c r="AI91" s="3">
         <v>-1400</v>
       </c>
       <c r="AJ91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8798,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8905,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-23800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-22600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-115100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>67400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-29300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-30800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-57300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-21400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-71000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-46100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-62700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-146900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>30000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>118600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-31700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-62600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>1600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-62000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-7600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-97900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>47000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-28200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-38400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-5500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>5300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,34 +9053,35 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E96" s="3">
         <v>9500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>9700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>8500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>9200</v>
-      </c>
-      <c r="H96" s="3">
-        <v>8500</v>
       </c>
       <c r="I96" s="3">
         <v>8500</v>
       </c>
       <c r="J96" s="3">
+        <v>8500</v>
+      </c>
+      <c r="K96" s="3">
         <v>7400</v>
-      </c>
-      <c r="K96" s="3">
-        <v>7200</v>
       </c>
       <c r="L96" s="3">
         <v>7200</v>
@@ -8855,14 +9089,14 @@
       <c r="M96" s="3">
         <v>7200</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>8</v>
+      <c r="N96" s="3">
+        <v>7200</v>
       </c>
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -8924,8 +9158,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9265,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9372,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,112 +9479,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-64800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-31600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-30300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-44400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-9600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-15900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-11000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-7400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-11700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-8800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-23300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-5100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-17600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1000</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9381,8 +9630,8 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -9442,110 +9691,116 @@
         <v>0</v>
       </c>
       <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>32800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-48500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-12900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>40000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>21900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-107100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>109900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-55100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>24100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>50700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-19600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-30400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-41700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-133500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>53600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>180300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-19700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>47600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-33400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>53600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-66800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>31300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>26000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>12300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>6400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>9000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>6100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1800</v>
       </c>
     </row>
